--- a/test/fpa/FPA预估2025版V3.xlsx
+++ b/test/fpa/FPA预估2025版V3.xlsx
@@ -1,10 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView windowWidth="20752" windowHeight="9555" activeTab="1"/>
+    <workbookView windowWidth="29100" windowHeight="13900" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="1. 填写说明" sheetId="5" r:id="rId1"/>
@@ -886,14 +886,6 @@
     </font>
     <font>
       <b/>
-      <sz val="26"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
       <sz val="12"/>
       <color theme="1"/>
       <name val="宋体"/>
@@ -924,6 +916,14 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="26"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="10"/>
       <color theme="1"/>
       <name val="宋体"/>
@@ -937,15 +937,15 @@
       <charset val="134"/>
     </font>
     <font>
+      <b/>
       <sz val="10"/>
-      <color rgb="FF0070C0"/>
+      <color indexed="8"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
-      <b/>
       <sz val="10"/>
-      <color indexed="8"/>
+      <color rgb="FF0070C0"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
@@ -990,18 +990,18 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="9"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
       <b/>
       <sz val="8"/>
       <color rgb="FFFF0000"/>
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="134"/>
     </font>
     <font>
       <sz val="9"/>
@@ -1182,12 +1182,12 @@
       <charset val="134"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -1685,10 +1685,10 @@
     <xf numFmtId="0" fontId="31" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="32" fillId="12" borderId="12" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
@@ -1805,67 +1805,67 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="3" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="3" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="5" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="0" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="4" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="176" fontId="0" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="6" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -1883,9 +1883,6 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="8" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1907,9 +1904,6 @@
     <xf numFmtId="178" fontId="7" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -1943,11 +1937,8 @@
     <xf numFmtId="176" fontId="7" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1955,6 +1946,15 @@
     <xf numFmtId="178" fontId="7" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
@@ -1976,88 +1976,91 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="179" fontId="13" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="179" fontId="15" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="179" fontId="13" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
     <xf numFmtId="0" fontId="14" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="179" fontId="15" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="18" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center"/>
@@ -2070,16 +2073,13 @@
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="18" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
@@ -2102,26 +2102,26 @@
       <alignment horizontal="left" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="176" fontId="4" fillId="5" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="176" fontId="3" fillId="5" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center"/>
       <protection locked="0"/>
     </xf>
@@ -2518,11 +2518,11 @@
     <tabColor theme="0" tint="-0.349986266670736"/>
   </sheetPr>
   <dimension ref="A1:B8"/>
-  <sheetFormatPr defaultColWidth="8.91150442477876" defaultRowHeight="12.75" outlineLevelRow="7" outlineLevelCol="1"/>
+  <sheetFormatPr defaultColWidth="8.91346153846154" defaultRowHeight="15.2" outlineLevelRow="7" outlineLevelCol="1"/>
   <cols>
-    <col min="1" max="1" customWidth="true" style="99" width="16.0" collapsed="false"/>
-    <col min="2" max="2" customWidth="true" style="99" width="149.451327433628" collapsed="false"/>
-    <col min="3" max="16384" style="99" width="8.91150442477876" collapsed="false"/>
+    <col min="1" max="1" width="16" style="99" customWidth="1"/>
+    <col min="2" max="2" width="149.451923076923" style="99" customWidth="1"/>
+    <col min="3" max="16384" width="8.91346153846154" style="99"/>
   </cols>
   <sheetData>
     <row r="1" ht="72.65" customHeight="1" spans="1:2">
@@ -2531,15 +2531,15 @@
       </c>
       <c r="B1" s="100"/>
     </row>
-    <row r="2" ht="15.75" spans="1:2">
+    <row r="2" ht="17.6" spans="1:2">
       <c r="A2" s="101"/>
       <c r="B2" s="101"/>
     </row>
-    <row r="3" ht="15.75" spans="1:2">
+    <row r="3" ht="17.6" spans="1:2">
       <c r="A3" s="102"/>
       <c r="B3" s="102"/>
     </row>
-    <row r="4" ht="15.75" spans="1:2">
+    <row r="4" ht="17.6" spans="1:2">
       <c r="A4" s="103" t="s">
         <v>1</v>
       </c>
@@ -2547,7 +2547,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="5" ht="15.75" spans="1:2">
+    <row r="5" ht="17.6" spans="1:2">
       <c r="A5" s="105" t="s">
         <v>3</v>
       </c>
@@ -2555,7 +2555,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="6" ht="15.75" spans="1:2">
+    <row r="6" ht="17.6" spans="1:2">
       <c r="A6" s="106" t="s">
         <v>5</v>
       </c>
@@ -2563,7 +2563,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="7" ht="15.75" spans="1:2">
+    <row r="7" ht="17.6" spans="1:2">
       <c r="A7" s="107" t="s">
         <v>7</v>
       </c>
@@ -2590,15 +2590,15 @@
     <tabColor rgb="FFFFFF00"/>
   </sheetPr>
   <dimension ref="A1:L84"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8"/>
   <cols>
-    <col min="1" max="1" customWidth="true" style="3" width="8.8141592920354" collapsed="false"/>
-    <col min="2" max="3" customWidth="true" width="19.8761061946903" collapsed="false"/>
-    <col min="4" max="4" customWidth="true" width="25.6283185840708" collapsed="false"/>
-    <col min="5" max="5" customWidth="true" width="26.7522123893805" collapsed="false"/>
-    <col min="6" max="6" customWidth="true" width="32.0" collapsed="false"/>
-    <col min="7" max="11" customWidth="true" style="3" width="8.8141592920354" collapsed="false"/>
-    <col min="12" max="12" customWidth="true" width="16.6283185840708" collapsed="false"/>
+    <col min="1" max="1" width="8.81730769230769" style="20" customWidth="1"/>
+    <col min="2" max="3" width="19.875" customWidth="1"/>
+    <col min="4" max="4" width="25.625" customWidth="1"/>
+    <col min="5" max="5" width="26.75" customWidth="1"/>
+    <col min="6" max="6" width="32" customWidth="1"/>
+    <col min="7" max="11" width="8.81730769230769" style="20" customWidth="1"/>
+    <col min="12" max="12" width="16.625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="42" customHeight="1" spans="1:12">
@@ -2630,141 +2630,141 @@
       </c>
       <c r="E3" s="64"/>
       <c r="F3" s="64"/>
-      <c r="G3" s="65"/>
-      <c r="H3" s="65"/>
-      <c r="I3" s="65"/>
-      <c r="J3" s="65"/>
-      <c r="K3" s="65"/>
+      <c r="G3" s="78"/>
+      <c r="H3" s="78"/>
+      <c r="I3" s="78"/>
+      <c r="J3" s="78"/>
+      <c r="K3" s="78"/>
       <c r="L3" s="64"/>
     </row>
     <row r="4" spans="1:12">
-      <c r="A4" s="66" t="s">
+      <c r="A4" s="65" t="s">
         <v>13</v>
       </c>
-      <c r="B4" s="67"/>
-      <c r="C4" s="68">
+      <c r="B4" s="66"/>
+      <c r="C4" s="67">
         <f>H84</f>
         <v>398</v>
       </c>
-      <c r="D4" s="69" t="s">
+      <c r="D4" s="68" t="s">
         <v>14</v>
       </c>
-      <c r="E4" s="69"/>
-      <c r="F4" s="69"/>
-      <c r="G4" s="70"/>
-      <c r="H4" s="70"/>
-      <c r="I4" s="70"/>
-      <c r="J4" s="70"/>
-      <c r="K4" s="70"/>
-      <c r="L4" s="69"/>
+      <c r="E4" s="68"/>
+      <c r="F4" s="68"/>
+      <c r="G4" s="79"/>
+      <c r="H4" s="79"/>
+      <c r="I4" s="79"/>
+      <c r="J4" s="79"/>
+      <c r="K4" s="79"/>
+      <c r="L4" s="68"/>
     </row>
     <row r="5" spans="1:12">
-      <c r="A5" s="66" t="s">
+      <c r="A5" s="65" t="s">
         <v>15</v>
       </c>
-      <c r="B5" s="67"/>
-      <c r="C5" s="71">
+      <c r="B5" s="66"/>
+      <c r="C5" s="69">
         <f>K84</f>
-        <v>122.6</v>
-      </c>
-      <c r="D5" s="69" t="s">
+        <v>125.266666666666</v>
+      </c>
+      <c r="D5" s="68" t="s">
         <v>16</v>
       </c>
-      <c r="E5" s="69"/>
-      <c r="F5" s="69"/>
-      <c r="G5" s="70"/>
-      <c r="H5" s="70"/>
-      <c r="I5" s="70"/>
-      <c r="J5" s="70"/>
-      <c r="K5" s="70"/>
-      <c r="L5" s="69"/>
+      <c r="E5" s="68"/>
+      <c r="F5" s="68"/>
+      <c r="G5" s="79"/>
+      <c r="H5" s="79"/>
+      <c r="I5" s="79"/>
+      <c r="J5" s="79"/>
+      <c r="K5" s="79"/>
+      <c r="L5" s="68"/>
     </row>
     <row r="6" ht="34" customHeight="1" spans="1:12">
-      <c r="A6" s="72" t="s">
+      <c r="A6" s="70" t="s">
         <v>17</v>
       </c>
-      <c r="B6" s="72"/>
-      <c r="C6" s="72"/>
-      <c r="D6" s="72"/>
-      <c r="E6" s="72"/>
-      <c r="F6" s="72"/>
-      <c r="G6" s="73"/>
-      <c r="H6" s="73"/>
-      <c r="I6" s="73"/>
-      <c r="J6" s="73"/>
-      <c r="K6" s="73"/>
-      <c r="L6" s="72"/>
-    </row>
-    <row r="7" s="52" customFormat="1" spans="1:12">
-      <c r="A7" s="74" t="s">
+      <c r="B6" s="70"/>
+      <c r="C6" s="70"/>
+      <c r="D6" s="70"/>
+      <c r="E6" s="70"/>
+      <c r="F6" s="70"/>
+      <c r="G6" s="80"/>
+      <c r="H6" s="80"/>
+      <c r="I6" s="80"/>
+      <c r="J6" s="80"/>
+      <c r="K6" s="80"/>
+      <c r="L6" s="70"/>
+    </row>
+    <row r="7" s="52" customFormat="1" ht="34" spans="1:12">
+      <c r="A7" s="71" t="s">
         <v>18</v>
       </c>
-      <c r="B7" s="75" t="s">
+      <c r="B7" s="72" t="s">
         <v>19</v>
       </c>
-      <c r="C7" s="75" t="s">
+      <c r="C7" s="72" t="s">
         <v>20</v>
       </c>
-      <c r="D7" s="75" t="s">
+      <c r="D7" s="72" t="s">
         <v>21</v>
       </c>
-      <c r="E7" s="75" t="s">
+      <c r="E7" s="72" t="s">
         <v>22</v>
       </c>
-      <c r="F7" s="75" t="s">
+      <c r="F7" s="72" t="s">
         <v>23</v>
       </c>
-      <c r="G7" s="74" t="s">
+      <c r="G7" s="71" t="s">
         <v>24</v>
       </c>
-      <c r="H7" s="74" t="s">
+      <c r="H7" s="71" t="s">
         <v>25</v>
       </c>
-      <c r="I7" s="74" t="s">
+      <c r="I7" s="71" t="s">
         <v>26</v>
       </c>
-      <c r="J7" s="74" t="s">
+      <c r="J7" s="71" t="s">
         <v>27</v>
       </c>
-      <c r="K7" s="74" t="s">
+      <c r="K7" s="71" t="s">
         <v>28</v>
       </c>
-      <c r="L7" s="75" t="s">
+      <c r="L7" s="72" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="8" s="53" customFormat="1" ht="30.4" spans="1:12">
-      <c r="A8" s="76" t="s">
+    <row r="8" s="53" customFormat="1" ht="36" spans="1:12">
+      <c r="A8" s="73" t="s">
         <v>30</v>
       </c>
-      <c r="B8" s="77" t="s">
+      <c r="B8" s="74" t="s">
         <v>31</v>
       </c>
-      <c r="C8" s="77" t="s">
+      <c r="C8" s="74" t="s">
         <v>31</v>
       </c>
-      <c r="D8" s="77" t="s">
+      <c r="D8" s="74" t="s">
         <v>31</v>
       </c>
-      <c r="E8" s="77" t="s">
+      <c r="E8" s="74" t="s">
         <v>31</v>
       </c>
-      <c r="F8" s="77" t="s">
+      <c r="F8" s="74" t="s">
         <v>31</v>
       </c>
-      <c r="G8" s="78" t="s">
+      <c r="G8" s="81" t="s">
         <v>32</v>
       </c>
-      <c r="H8" s="78" t="s">
+      <c r="H8" s="81" t="s">
         <v>33</v>
       </c>
-      <c r="I8" s="78" t="s">
+      <c r="I8" s="81" t="s">
         <v>34</v>
       </c>
-      <c r="J8" s="78" t="s">
+      <c r="J8" s="81" t="s">
         <v>35</v>
       </c>
-      <c r="K8" s="78" t="s">
+      <c r="K8" s="81" t="s">
         <v>36</v>
       </c>
       <c r="L8" s="87" t="s">
@@ -2772,28 +2772,28 @@
       </c>
     </row>
     <row r="9" s="54" customFormat="1" spans="1:12">
-      <c r="A9" s="79">
+      <c r="A9" s="75">
         <v>1</v>
       </c>
-      <c r="B9" s="80" t="s">
-        <v>38</v>
-      </c>
-      <c r="C9" s="80" t="s">
-        <v>39</v>
-      </c>
-      <c r="D9" s="80" t="s">
-        <v>40</v>
-      </c>
-      <c r="E9" s="80" t="s">
-        <v>40</v>
-      </c>
-      <c r="F9" s="81" t="s">
+      <c r="B9" s="76" t="s">
+        <v>38</v>
+      </c>
+      <c r="C9" s="76" t="s">
+        <v>39</v>
+      </c>
+      <c r="D9" s="76" t="s">
+        <v>40</v>
+      </c>
+      <c r="E9" s="76" t="s">
+        <v>40</v>
+      </c>
+      <c r="F9" s="82" t="s">
         <v>41</v>
       </c>
-      <c r="G9" s="82" t="s">
+      <c r="G9" s="83" t="s">
         <v>42</v>
       </c>
-      <c r="H9" s="83">
+      <c r="H9" s="84">
         <f>IF(G9="ILF",'3. 调整因子'!$D$63,IF(G9="EIF",'3. 调整因子'!$D$64,IF(G9="EI",'3. 调整因子'!$D$65,IF(G9="EO",'3. 调整因子'!$D$66,IF(G9="EQ",'3. 调整因子'!$D$67,"")))))</f>
         <v>4</v>
       </c>
@@ -2804,33 +2804,34 @@
         <v>44</v>
       </c>
       <c r="K9" s="89">
-        <v>0</v>
+        <f>IF(H9="","",IF(I9="高",IF(J9="删除",H9*'3. 调整因子'!$D$53*'3. 调整因子'!$D$60,IF(J9="修改",H9*'3. 调整因子'!$D$53*'3. 调整因子'!$D$59,H9*'3. 调整因子'!$D$53*'3. 调整因子'!$D$58)),IF(I9="中",IF(J9="删除",H9*'3. 调整因子'!$D$54*'3. 调整因子'!$D$60,IF(J9="修改",H9*'3. 调整因子'!$D$54*'3. 调整因子'!$D$59,H9*'3. 调整因子'!$D$54*'3. 调整因子'!$D$58)),IF(J9="删除",H9*'3. 调整因子'!$D$55*'3. 调整因子'!$D$60,IF(J9="修改",H9*'3. 调整因子'!$D$55*'3. 调整因子'!$D$59,H9*'3. 调整因子'!$D$55*'3. 调整因子'!$D$58)))))</f>
+        <v>1.33333333333333</v>
       </c>
       <c r="L9" s="90"/>
     </row>
     <row r="10" s="54" customFormat="1" spans="1:12">
-      <c r="A10" s="79">
+      <c r="A10" s="75">
         <v>2</v>
       </c>
-      <c r="B10" s="80" t="s">
-        <v>38</v>
-      </c>
-      <c r="C10" s="80" t="s">
-        <v>39</v>
-      </c>
-      <c r="D10" s="80" t="s">
-        <v>40</v>
-      </c>
-      <c r="E10" s="80" t="s">
-        <v>40</v>
-      </c>
-      <c r="F10" s="81" t="s">
+      <c r="B10" s="76" t="s">
+        <v>38</v>
+      </c>
+      <c r="C10" s="76" t="s">
+        <v>39</v>
+      </c>
+      <c r="D10" s="76" t="s">
+        <v>40</v>
+      </c>
+      <c r="E10" s="76" t="s">
+        <v>40</v>
+      </c>
+      <c r="F10" s="82" t="s">
         <v>45</v>
       </c>
-      <c r="G10" s="82" t="s">
+      <c r="G10" s="83" t="s">
         <v>42</v>
       </c>
-      <c r="H10" s="83">
+      <c r="H10" s="84">
         <f>IF(G10="ILF",'3. 调整因子'!$D$63,IF(G10="EIF",'3. 调整因子'!$D$64,IF(G10="EI",'3. 调整因子'!$D$65,IF(G10="EO",'3. 调整因子'!$D$66,IF(G10="EQ",'3. 调整因子'!$D$67,"")))))</f>
         <v>4</v>
       </c>
@@ -2841,33 +2842,34 @@
         <v>44</v>
       </c>
       <c r="K10" s="89">
-        <v>0</v>
+        <f>IF(H10="","",IF(I10="高",IF(J10="删除",H10*'3. 调整因子'!$D$53*'3. 调整因子'!$D$60,IF(J10="修改",H10*'3. 调整因子'!$D$53*'3. 调整因子'!$D$59,H10*'3. 调整因子'!$D$53*'3. 调整因子'!$D$58)),IF(I10="中",IF(J10="删除",H10*'3. 调整因子'!$D$54*'3. 调整因子'!$D$60,IF(J10="修改",H10*'3. 调整因子'!$D$54*'3. 调整因子'!$D$59,H10*'3. 调整因子'!$D$54*'3. 调整因子'!$D$58)),IF(J10="删除",H10*'3. 调整因子'!$D$55*'3. 调整因子'!$D$60,IF(J10="修改",H10*'3. 调整因子'!$D$55*'3. 调整因子'!$D$59,H10*'3. 调整因子'!$D$55*'3. 调整因子'!$D$58)))))</f>
+        <v>1.33333333333333</v>
       </c>
       <c r="L10" s="90"/>
     </row>
     <row r="11" s="54" customFormat="1" spans="1:12">
-      <c r="A11" s="79">
+      <c r="A11" s="75">
         <v>3</v>
       </c>
-      <c r="B11" s="80" t="s">
-        <v>38</v>
-      </c>
-      <c r="C11" s="80" t="s">
-        <v>39</v>
-      </c>
-      <c r="D11" s="80" t="s">
-        <v>40</v>
-      </c>
-      <c r="E11" s="80" t="s">
-        <v>40</v>
-      </c>
-      <c r="F11" s="81" t="s">
+      <c r="B11" s="76" t="s">
+        <v>38</v>
+      </c>
+      <c r="C11" s="76" t="s">
+        <v>39</v>
+      </c>
+      <c r="D11" s="76" t="s">
+        <v>40</v>
+      </c>
+      <c r="E11" s="76" t="s">
+        <v>40</v>
+      </c>
+      <c r="F11" s="82" t="s">
         <v>46</v>
       </c>
-      <c r="G11" s="82" t="s">
+      <c r="G11" s="83" t="s">
         <v>47</v>
       </c>
-      <c r="H11" s="83">
+      <c r="H11" s="84">
         <f>IF(G11="ILF",'3. 调整因子'!$D$63,IF(G11="EIF",'3. 调整因子'!$D$64,IF(G11="EI",'3. 调整因子'!$D$65,IF(G11="EO",'3. 调整因子'!$D$66,IF(G11="EQ",'3. 调整因子'!$D$67,"")))))</f>
         <v>5</v>
       </c>
@@ -2884,28 +2886,28 @@
       <c r="L11" s="90"/>
     </row>
     <row r="12" s="54" customFormat="1" spans="1:12">
-      <c r="A12" s="79">
+      <c r="A12" s="75">
         <v>4</v>
       </c>
-      <c r="B12" s="80" t="s">
-        <v>38</v>
-      </c>
-      <c r="C12" s="80" t="s">
-        <v>39</v>
-      </c>
-      <c r="D12" s="80" t="s">
-        <v>40</v>
-      </c>
-      <c r="E12" s="80" t="s">
-        <v>40</v>
-      </c>
-      <c r="F12" s="81" t="s">
+      <c r="B12" s="76" t="s">
+        <v>38</v>
+      </c>
+      <c r="C12" s="76" t="s">
+        <v>39</v>
+      </c>
+      <c r="D12" s="76" t="s">
+        <v>40</v>
+      </c>
+      <c r="E12" s="76" t="s">
+        <v>40</v>
+      </c>
+      <c r="F12" s="82" t="s">
         <v>48</v>
       </c>
-      <c r="G12" s="82" t="s">
+      <c r="G12" s="83" t="s">
         <v>47</v>
       </c>
-      <c r="H12" s="83">
+      <c r="H12" s="84">
         <f>IF(G12="ILF",'3. 调整因子'!$D$63,IF(G12="EIF",'3. 调整因子'!$D$64,IF(G12="EI",'3. 调整因子'!$D$65,IF(G12="EO",'3. 调整因子'!$D$66,IF(G12="EQ",'3. 调整因子'!$D$67,"")))))</f>
         <v>5</v>
       </c>
@@ -2922,28 +2924,28 @@
       <c r="L12" s="90"/>
     </row>
     <row r="13" s="55" customFormat="1" spans="1:12">
-      <c r="A13" s="79">
+      <c r="A13" s="75">
         <v>5</v>
       </c>
-      <c r="B13" s="80" t="s">
-        <v>38</v>
-      </c>
-      <c r="C13" s="80" t="s">
-        <v>39</v>
-      </c>
-      <c r="D13" s="80" t="s">
-        <v>40</v>
-      </c>
-      <c r="E13" s="80" t="s">
-        <v>40</v>
-      </c>
-      <c r="F13" s="81" t="s">
+      <c r="B13" s="76" t="s">
+        <v>38</v>
+      </c>
+      <c r="C13" s="76" t="s">
+        <v>39</v>
+      </c>
+      <c r="D13" s="76" t="s">
+        <v>40</v>
+      </c>
+      <c r="E13" s="76" t="s">
+        <v>40</v>
+      </c>
+      <c r="F13" s="82" t="s">
         <v>50</v>
       </c>
-      <c r="G13" s="82" t="s">
+      <c r="G13" s="83" t="s">
         <v>51</v>
       </c>
-      <c r="H13" s="83">
+      <c r="H13" s="84">
         <f>IF(G13="ILF",'3. 调整因子'!$D$63,IF(G13="EIF",'3. 调整因子'!$D$64,IF(G13="EI",'3. 调整因子'!$D$65,IF(G13="EO",'3. 调整因子'!$D$66,IF(G13="EQ",'3. 调整因子'!$D$67,"")))))</f>
         <v>7</v>
       </c>
@@ -2960,28 +2962,28 @@
       <c r="L13" s="90"/>
     </row>
     <row r="14" s="56" customFormat="1" spans="1:12">
-      <c r="A14" s="79">
+      <c r="A14" s="75">
         <v>6</v>
       </c>
-      <c r="B14" s="84" t="s">
-        <v>38</v>
-      </c>
-      <c r="C14" s="84" t="s">
-        <v>39</v>
-      </c>
-      <c r="D14" s="84" t="s">
-        <v>40</v>
-      </c>
-      <c r="E14" s="84" t="s">
-        <v>40</v>
-      </c>
-      <c r="F14" s="81" t="s">
+      <c r="B14" s="77" t="s">
+        <v>38</v>
+      </c>
+      <c r="C14" s="77" t="s">
+        <v>39</v>
+      </c>
+      <c r="D14" s="77" t="s">
+        <v>40</v>
+      </c>
+      <c r="E14" s="77" t="s">
+        <v>40</v>
+      </c>
+      <c r="F14" s="82" t="s">
         <v>52</v>
       </c>
-      <c r="G14" s="82" t="s">
+      <c r="G14" s="83" t="s">
         <v>51</v>
       </c>
-      <c r="H14" s="83">
+      <c r="H14" s="84">
         <f>IF(G14="ILF",'3. 调整因子'!$D$63,IF(G14="EIF",'3. 调整因子'!$D$64,IF(G14="EI",'3. 调整因子'!$D$65,IF(G14="EO",'3. 调整因子'!$D$66,IF(G14="EQ",'3. 调整因子'!$D$67,"")))))</f>
         <v>7</v>
       </c>
@@ -2998,28 +3000,28 @@
       <c r="L14" s="92"/>
     </row>
     <row r="15" spans="1:12">
-      <c r="A15" s="79">
+      <c r="A15" s="75">
         <v>7</v>
       </c>
-      <c r="B15" s="80" t="s">
-        <v>38</v>
-      </c>
-      <c r="C15" s="80" t="s">
-        <v>39</v>
-      </c>
-      <c r="D15" s="80" t="s">
-        <v>40</v>
-      </c>
-      <c r="E15" s="80" t="s">
-        <v>40</v>
-      </c>
-      <c r="F15" s="81" t="s">
+      <c r="B15" s="76" t="s">
+        <v>38</v>
+      </c>
+      <c r="C15" s="76" t="s">
+        <v>39</v>
+      </c>
+      <c r="D15" s="76" t="s">
+        <v>40</v>
+      </c>
+      <c r="E15" s="76" t="s">
+        <v>40</v>
+      </c>
+      <c r="F15" s="82" t="s">
         <v>53</v>
       </c>
-      <c r="G15" s="82" t="s">
+      <c r="G15" s="83" t="s">
         <v>54</v>
       </c>
-      <c r="H15" s="83">
+      <c r="H15" s="84">
         <f>IF(G15="ILF",'3. 调整因子'!$D$63,IF(G15="EIF",'3. 调整因子'!$D$64,IF(G15="EI",'3. 调整因子'!$D$65,IF(G15="EO",'3. 调整因子'!$D$66,IF(G15="EQ",'3. 调整因子'!$D$67,"")))))</f>
         <v>4</v>
       </c>
@@ -3036,28 +3038,28 @@
       <c r="L15" s="90"/>
     </row>
     <row r="16" spans="1:12">
-      <c r="A16" s="79">
+      <c r="A16" s="75">
         <v>8</v>
       </c>
-      <c r="B16" s="80" t="s">
-        <v>38</v>
-      </c>
-      <c r="C16" s="80" t="s">
-        <v>39</v>
-      </c>
-      <c r="D16" s="80" t="s">
-        <v>40</v>
-      </c>
-      <c r="E16" s="80" t="s">
+      <c r="B16" s="76" t="s">
+        <v>38</v>
+      </c>
+      <c r="C16" s="76" t="s">
+        <v>39</v>
+      </c>
+      <c r="D16" s="76" t="s">
+        <v>40</v>
+      </c>
+      <c r="E16" s="76" t="s">
         <v>40</v>
       </c>
       <c r="F16" s="85" t="s">
         <v>55</v>
       </c>
-      <c r="G16" s="82" t="s">
+      <c r="G16" s="83" t="s">
         <v>47</v>
       </c>
-      <c r="H16" s="83">
+      <c r="H16" s="84">
         <f>IF(G16="ILF",'3. 调整因子'!$D$63,IF(G16="EIF",'3. 调整因子'!$D$64,IF(G16="EI",'3. 调整因子'!$D$65,IF(G16="EO",'3. 调整因子'!$D$66,IF(G16="EQ",'3. 调整因子'!$D$67,"")))))</f>
         <v>5</v>
       </c>
@@ -3074,28 +3076,28 @@
       <c r="L16" s="90"/>
     </row>
     <row r="17" s="56" customFormat="1" spans="1:12">
-      <c r="A17" s="79">
+      <c r="A17" s="75">
         <v>9</v>
       </c>
-      <c r="B17" s="84" t="s">
-        <v>38</v>
-      </c>
-      <c r="C17" s="84" t="s">
-        <v>39</v>
-      </c>
-      <c r="D17" s="84" t="s">
-        <v>40</v>
-      </c>
-      <c r="E17" s="84" t="s">
-        <v>40</v>
-      </c>
-      <c r="F17" s="81" t="s">
+      <c r="B17" s="77" t="s">
+        <v>38</v>
+      </c>
+      <c r="C17" s="77" t="s">
+        <v>39</v>
+      </c>
+      <c r="D17" s="77" t="s">
+        <v>40</v>
+      </c>
+      <c r="E17" s="77" t="s">
+        <v>40</v>
+      </c>
+      <c r="F17" s="82" t="s">
         <v>56</v>
       </c>
-      <c r="G17" s="82" t="s">
+      <c r="G17" s="83" t="s">
         <v>51</v>
       </c>
-      <c r="H17" s="83">
+      <c r="H17" s="84">
         <f>IF(G17="ILF",'3. 调整因子'!$D$63,IF(G17="EIF",'3. 调整因子'!$D$64,IF(G17="EI",'3. 调整因子'!$D$65,IF(G17="EO",'3. 调整因子'!$D$66,IF(G17="EQ",'3. 调整因子'!$D$67,"")))))</f>
         <v>7</v>
       </c>
@@ -3112,28 +3114,28 @@
       <c r="L17" s="92"/>
     </row>
     <row r="18" s="54" customFormat="1" spans="1:12">
-      <c r="A18" s="79">
+      <c r="A18" s="75">
         <v>10</v>
       </c>
-      <c r="B18" s="80" t="s">
-        <v>38</v>
-      </c>
-      <c r="C18" s="80" t="s">
-        <v>39</v>
-      </c>
-      <c r="D18" s="80" t="s">
-        <v>40</v>
-      </c>
-      <c r="E18" s="80" t="s">
-        <v>40</v>
-      </c>
-      <c r="F18" s="81" t="s">
+      <c r="B18" s="76" t="s">
+        <v>38</v>
+      </c>
+      <c r="C18" s="76" t="s">
+        <v>39</v>
+      </c>
+      <c r="D18" s="76" t="s">
+        <v>40</v>
+      </c>
+      <c r="E18" s="76" t="s">
+        <v>40</v>
+      </c>
+      <c r="F18" s="82" t="s">
         <v>57</v>
       </c>
-      <c r="G18" s="82" t="s">
+      <c r="G18" s="83" t="s">
         <v>54</v>
       </c>
-      <c r="H18" s="83">
+      <c r="H18" s="84">
         <f>IF(G18="ILF",'3. 调整因子'!$D$63,IF(G18="EIF",'3. 调整因子'!$D$64,IF(G18="EI",'3. 调整因子'!$D$65,IF(G18="EO",'3. 调整因子'!$D$66,IF(G18="EQ",'3. 调整因子'!$D$67,"")))))</f>
         <v>4</v>
       </c>
@@ -3149,28 +3151,28 @@
       <c r="L18" s="90"/>
     </row>
     <row r="19" s="54" customFormat="1" spans="1:12">
-      <c r="A19" s="79">
+      <c r="A19" s="75">
         <v>11</v>
       </c>
-      <c r="B19" s="80" t="s">
-        <v>38</v>
-      </c>
-      <c r="C19" s="80" t="s">
-        <v>39</v>
-      </c>
-      <c r="D19" s="80" t="s">
-        <v>40</v>
-      </c>
-      <c r="E19" s="80" t="s">
-        <v>40</v>
-      </c>
-      <c r="F19" s="81" t="s">
+      <c r="B19" s="76" t="s">
+        <v>38</v>
+      </c>
+      <c r="C19" s="76" t="s">
+        <v>39</v>
+      </c>
+      <c r="D19" s="76" t="s">
+        <v>40</v>
+      </c>
+      <c r="E19" s="76" t="s">
+        <v>40</v>
+      </c>
+      <c r="F19" s="82" t="s">
         <v>58</v>
       </c>
-      <c r="G19" s="82" t="s">
+      <c r="G19" s="83" t="s">
         <v>47</v>
       </c>
-      <c r="H19" s="83">
+      <c r="H19" s="84">
         <f>IF(G19="ILF",'3. 调整因子'!$D$63,IF(G19="EIF",'3. 调整因子'!$D$64,IF(G19="EI",'3. 调整因子'!$D$65,IF(G19="EO",'3. 调整因子'!$D$66,IF(G19="EQ",'3. 调整因子'!$D$67,"")))))</f>
         <v>5</v>
       </c>
@@ -3187,28 +3189,28 @@
       <c r="L19" s="90"/>
     </row>
     <row r="20" s="56" customFormat="1" spans="1:12">
-      <c r="A20" s="79">
+      <c r="A20" s="75">
         <v>12</v>
       </c>
-      <c r="B20" s="84" t="s">
-        <v>38</v>
-      </c>
-      <c r="C20" s="84" t="s">
-        <v>39</v>
-      </c>
-      <c r="D20" s="84" t="s">
-        <v>40</v>
-      </c>
-      <c r="E20" s="84" t="s">
-        <v>40</v>
-      </c>
-      <c r="F20" s="81" t="s">
+      <c r="B20" s="77" t="s">
+        <v>38</v>
+      </c>
+      <c r="C20" s="77" t="s">
+        <v>39</v>
+      </c>
+      <c r="D20" s="77" t="s">
+        <v>40</v>
+      </c>
+      <c r="E20" s="77" t="s">
+        <v>40</v>
+      </c>
+      <c r="F20" s="82" t="s">
         <v>59</v>
       </c>
-      <c r="G20" s="82" t="s">
+      <c r="G20" s="83" t="s">
         <v>51</v>
       </c>
-      <c r="H20" s="83">
+      <c r="H20" s="84">
         <f>IF(G20="ILF",'3. 调整因子'!$D$63,IF(G20="EIF",'3. 调整因子'!$D$64,IF(G20="EI",'3. 调整因子'!$D$65,IF(G20="EO",'3. 调整因子'!$D$66,IF(G20="EQ",'3. 调整因子'!$D$67,"")))))</f>
         <v>7</v>
       </c>
@@ -3225,28 +3227,28 @@
       <c r="L20" s="92"/>
     </row>
     <row r="21" s="54" customFormat="1" spans="1:12">
-      <c r="A21" s="79">
+      <c r="A21" s="75">
         <v>13</v>
       </c>
-      <c r="B21" s="80" t="s">
-        <v>38</v>
-      </c>
-      <c r="C21" s="80" t="s">
-        <v>39</v>
-      </c>
-      <c r="D21" s="80" t="s">
-        <v>40</v>
-      </c>
-      <c r="E21" s="80" t="s">
-        <v>40</v>
-      </c>
-      <c r="F21" s="81" t="s">
+      <c r="B21" s="76" t="s">
+        <v>38</v>
+      </c>
+      <c r="C21" s="76" t="s">
+        <v>39</v>
+      </c>
+      <c r="D21" s="76" t="s">
+        <v>40</v>
+      </c>
+      <c r="E21" s="76" t="s">
+        <v>40</v>
+      </c>
+      <c r="F21" s="82" t="s">
         <v>60</v>
       </c>
-      <c r="G21" s="82" t="s">
+      <c r="G21" s="83" t="s">
         <v>47</v>
       </c>
-      <c r="H21" s="83">
+      <c r="H21" s="84">
         <f>IF(G21="ILF",'3. 调整因子'!$D$63,IF(G21="EIF",'3. 调整因子'!$D$64,IF(G21="EI",'3. 调整因子'!$D$65,IF(G21="EO",'3. 调整因子'!$D$66,IF(G21="EQ",'3. 调整因子'!$D$67,"")))))</f>
         <v>5</v>
       </c>
@@ -3262,28 +3264,28 @@
       <c r="L21" s="90"/>
     </row>
     <row r="22" s="54" customFormat="1" spans="1:12">
-      <c r="A22" s="79">
+      <c r="A22" s="75">
         <v>14</v>
       </c>
-      <c r="B22" s="80" t="s">
-        <v>38</v>
-      </c>
-      <c r="C22" s="80" t="s">
-        <v>39</v>
-      </c>
-      <c r="D22" s="80" t="s">
-        <v>40</v>
-      </c>
-      <c r="E22" s="80" t="s">
-        <v>40</v>
-      </c>
-      <c r="F22" s="81" t="s">
+      <c r="B22" s="76" t="s">
+        <v>38</v>
+      </c>
+      <c r="C22" s="76" t="s">
+        <v>39</v>
+      </c>
+      <c r="D22" s="76" t="s">
+        <v>40</v>
+      </c>
+      <c r="E22" s="76" t="s">
+        <v>40</v>
+      </c>
+      <c r="F22" s="82" t="s">
         <v>61</v>
       </c>
-      <c r="G22" s="82" t="s">
+      <c r="G22" s="83" t="s">
         <v>47</v>
       </c>
-      <c r="H22" s="83">
+      <c r="H22" s="84">
         <f>IF(G22="ILF",'3. 调整因子'!$D$63,IF(G22="EIF",'3. 调整因子'!$D$64,IF(G22="EI",'3. 调整因子'!$D$65,IF(G22="EO",'3. 调整因子'!$D$66,IF(G22="EQ",'3. 调整因子'!$D$67,"")))))</f>
         <v>5</v>
       </c>
@@ -3299,28 +3301,28 @@
       <c r="L22" s="90"/>
     </row>
     <row r="23" s="54" customFormat="1" spans="1:12">
-      <c r="A23" s="79">
+      <c r="A23" s="75">
         <v>15</v>
       </c>
-      <c r="B23" s="80" t="s">
-        <v>38</v>
-      </c>
-      <c r="C23" s="80" t="s">
-        <v>39</v>
-      </c>
-      <c r="D23" s="80" t="s">
-        <v>40</v>
-      </c>
-      <c r="E23" s="80" t="s">
-        <v>40</v>
-      </c>
-      <c r="F23" s="81" t="s">
+      <c r="B23" s="76" t="s">
+        <v>38</v>
+      </c>
+      <c r="C23" s="76" t="s">
+        <v>39</v>
+      </c>
+      <c r="D23" s="76" t="s">
+        <v>40</v>
+      </c>
+      <c r="E23" s="76" t="s">
+        <v>40</v>
+      </c>
+      <c r="F23" s="82" t="s">
         <v>62</v>
       </c>
-      <c r="G23" s="82" t="s">
+      <c r="G23" s="83" t="s">
         <v>47</v>
       </c>
-      <c r="H23" s="83">
+      <c r="H23" s="84">
         <f>IF(G23="ILF",'3. 调整因子'!$D$63,IF(G23="EIF",'3. 调整因子'!$D$64,IF(G23="EI",'3. 调整因子'!$D$65,IF(G23="EO",'3. 调整因子'!$D$66,IF(G23="EQ",'3. 调整因子'!$D$67,"")))))</f>
         <v>5</v>
       </c>
@@ -3337,28 +3339,28 @@
       <c r="L23" s="90"/>
     </row>
     <row r="24" s="54" customFormat="1" spans="1:12">
-      <c r="A24" s="79">
+      <c r="A24" s="75">
         <v>16</v>
       </c>
-      <c r="B24" s="80" t="s">
-        <v>38</v>
-      </c>
-      <c r="C24" s="80" t="s">
-        <v>39</v>
-      </c>
-      <c r="D24" s="80" t="s">
-        <v>40</v>
-      </c>
-      <c r="E24" s="80" t="s">
-        <v>40</v>
-      </c>
-      <c r="F24" s="81" t="s">
+      <c r="B24" s="76" t="s">
+        <v>38</v>
+      </c>
+      <c r="C24" s="76" t="s">
+        <v>39</v>
+      </c>
+      <c r="D24" s="76" t="s">
+        <v>40</v>
+      </c>
+      <c r="E24" s="76" t="s">
+        <v>40</v>
+      </c>
+      <c r="F24" s="82" t="s">
         <v>63</v>
       </c>
-      <c r="G24" s="82" t="s">
+      <c r="G24" s="83" t="s">
         <v>47</v>
       </c>
-      <c r="H24" s="83">
+      <c r="H24" s="84">
         <f>IF(G24="ILF",'3. 调整因子'!$D$63,IF(G24="EIF",'3. 调整因子'!$D$64,IF(G24="EI",'3. 调整因子'!$D$65,IF(G24="EO",'3. 调整因子'!$D$66,IF(G24="EQ",'3. 调整因子'!$D$67,"")))))</f>
         <v>5</v>
       </c>
@@ -3375,28 +3377,28 @@
       <c r="L24" s="90"/>
     </row>
     <row r="25" s="54" customFormat="1" spans="1:12">
-      <c r="A25" s="79">
+      <c r="A25" s="75">
         <v>17</v>
       </c>
-      <c r="B25" s="80" t="s">
-        <v>38</v>
-      </c>
-      <c r="C25" s="80" t="s">
-        <v>39</v>
-      </c>
-      <c r="D25" s="80" t="s">
-        <v>40</v>
-      </c>
-      <c r="E25" s="80" t="s">
-        <v>40</v>
-      </c>
-      <c r="F25" s="81" t="s">
+      <c r="B25" s="76" t="s">
+        <v>38</v>
+      </c>
+      <c r="C25" s="76" t="s">
+        <v>39</v>
+      </c>
+      <c r="D25" s="76" t="s">
+        <v>40</v>
+      </c>
+      <c r="E25" s="76" t="s">
+        <v>40</v>
+      </c>
+      <c r="F25" s="82" t="s">
         <v>64</v>
       </c>
-      <c r="G25" s="82" t="s">
+      <c r="G25" s="83" t="s">
         <v>47</v>
       </c>
-      <c r="H25" s="83">
+      <c r="H25" s="84">
         <f>IF(G25="ILF",'3. 调整因子'!$D$63,IF(G25="EIF",'3. 调整因子'!$D$64,IF(G25="EI",'3. 调整因子'!$D$65,IF(G25="EO",'3. 调整因子'!$D$66,IF(G25="EQ",'3. 调整因子'!$D$67,"")))))</f>
         <v>5</v>
       </c>
@@ -3413,28 +3415,28 @@
       <c r="L25" s="90"/>
     </row>
     <row r="26" s="54" customFormat="1" spans="1:12">
-      <c r="A26" s="79">
+      <c r="A26" s="75">
         <v>18</v>
       </c>
-      <c r="B26" s="80" t="s">
-        <v>38</v>
-      </c>
-      <c r="C26" s="80" t="s">
-        <v>39</v>
-      </c>
-      <c r="D26" s="80" t="s">
-        <v>40</v>
-      </c>
-      <c r="E26" s="80" t="s">
-        <v>40</v>
-      </c>
-      <c r="F26" s="81" t="s">
+      <c r="B26" s="76" t="s">
+        <v>38</v>
+      </c>
+      <c r="C26" s="76" t="s">
+        <v>39</v>
+      </c>
+      <c r="D26" s="76" t="s">
+        <v>40</v>
+      </c>
+      <c r="E26" s="76" t="s">
+        <v>40</v>
+      </c>
+      <c r="F26" s="82" t="s">
         <v>65</v>
       </c>
-      <c r="G26" s="82" t="s">
+      <c r="G26" s="83" t="s">
         <v>47</v>
       </c>
-      <c r="H26" s="83">
+      <c r="H26" s="84">
         <f>IF(G26="ILF",'3. 调整因子'!$D$63,IF(G26="EIF",'3. 调整因子'!$D$64,IF(G26="EI",'3. 调整因子'!$D$65,IF(G26="EO",'3. 调整因子'!$D$66,IF(G26="EQ",'3. 调整因子'!$D$67,"")))))</f>
         <v>5</v>
       </c>
@@ -3451,28 +3453,28 @@
       <c r="L26" s="90"/>
     </row>
     <row r="27" spans="1:12">
-      <c r="A27" s="79">
+      <c r="A27" s="75">
         <v>19</v>
       </c>
-      <c r="B27" s="80" t="s">
-        <v>38</v>
-      </c>
-      <c r="C27" s="80" t="s">
-        <v>39</v>
-      </c>
-      <c r="D27" s="80" t="s">
-        <v>40</v>
-      </c>
-      <c r="E27" s="80" t="s">
-        <v>40</v>
-      </c>
-      <c r="F27" s="81" t="s">
+      <c r="B27" s="76" t="s">
+        <v>38</v>
+      </c>
+      <c r="C27" s="76" t="s">
+        <v>39</v>
+      </c>
+      <c r="D27" s="76" t="s">
+        <v>40</v>
+      </c>
+      <c r="E27" s="76" t="s">
+        <v>40</v>
+      </c>
+      <c r="F27" s="82" t="s">
         <v>66</v>
       </c>
-      <c r="G27" s="82" t="s">
+      <c r="G27" s="83" t="s">
         <v>47</v>
       </c>
-      <c r="H27" s="83">
+      <c r="H27" s="84">
         <f>IF(G27="ILF",'3. 调整因子'!$D$63,IF(G27="EIF",'3. 调整因子'!$D$64,IF(G27="EI",'3. 调整因子'!$D$65,IF(G27="EO",'3. 调整因子'!$D$66,IF(G27="EQ",'3. 调整因子'!$D$67,"")))))</f>
         <v>5</v>
       </c>
@@ -3489,28 +3491,28 @@
       <c r="L27" s="90"/>
     </row>
     <row r="28" s="57" customFormat="1" spans="1:12">
-      <c r="A28" s="79">
+      <c r="A28" s="75">
         <v>20</v>
       </c>
-      <c r="B28" s="80" t="s">
-        <v>38</v>
-      </c>
-      <c r="C28" s="80" t="s">
-        <v>39</v>
-      </c>
-      <c r="D28" s="80" t="s">
-        <v>40</v>
-      </c>
-      <c r="E28" s="80" t="s">
-        <v>40</v>
-      </c>
-      <c r="F28" s="81" t="s">
+      <c r="B28" s="76" t="s">
+        <v>38</v>
+      </c>
+      <c r="C28" s="76" t="s">
+        <v>39</v>
+      </c>
+      <c r="D28" s="76" t="s">
+        <v>40</v>
+      </c>
+      <c r="E28" s="76" t="s">
+        <v>40</v>
+      </c>
+      <c r="F28" s="82" t="s">
         <v>67</v>
       </c>
-      <c r="G28" s="82" t="s">
+      <c r="G28" s="83" t="s">
         <v>47</v>
       </c>
-      <c r="H28" s="83">
+      <c r="H28" s="84">
         <f>IF(G28="ILF",'3. 调整因子'!$D$63,IF(G28="EIF",'3. 调整因子'!$D$64,IF(G28="EI",'3. 调整因子'!$D$65,IF(G28="EO",'3. 调整因子'!$D$66,IF(G28="EQ",'3. 调整因子'!$D$67,"")))))</f>
         <v>5</v>
       </c>
@@ -3527,28 +3529,28 @@
       <c r="L28" s="90"/>
     </row>
     <row r="29" s="56" customFormat="1" spans="1:12">
-      <c r="A29" s="79">
+      <c r="A29" s="75">
         <v>21</v>
       </c>
-      <c r="B29" s="84" t="s">
-        <v>38</v>
-      </c>
-      <c r="C29" s="84" t="s">
-        <v>39</v>
-      </c>
-      <c r="D29" s="84" t="s">
-        <v>40</v>
-      </c>
-      <c r="E29" s="84" t="s">
-        <v>40</v>
-      </c>
-      <c r="F29" s="81" t="s">
+      <c r="B29" s="77" t="s">
+        <v>38</v>
+      </c>
+      <c r="C29" s="77" t="s">
+        <v>39</v>
+      </c>
+      <c r="D29" s="77" t="s">
+        <v>40</v>
+      </c>
+      <c r="E29" s="77" t="s">
+        <v>40</v>
+      </c>
+      <c r="F29" s="82" t="s">
         <v>68</v>
       </c>
-      <c r="G29" s="82" t="s">
+      <c r="G29" s="83" t="s">
         <v>51</v>
       </c>
-      <c r="H29" s="83">
+      <c r="H29" s="84">
         <f>IF(G29="ILF",'3. 调整因子'!$D$63,IF(G29="EIF",'3. 调整因子'!$D$64,IF(G29="EI",'3. 调整因子'!$D$65,IF(G29="EO",'3. 调整因子'!$D$66,IF(G29="EQ",'3. 调整因子'!$D$67,"")))))</f>
         <v>7</v>
       </c>
@@ -3565,28 +3567,28 @@
       <c r="L29" s="92"/>
     </row>
     <row r="30" s="56" customFormat="1" spans="1:12">
-      <c r="A30" s="79">
+      <c r="A30" s="75">
         <v>22</v>
       </c>
-      <c r="B30" s="84" t="s">
-        <v>38</v>
-      </c>
-      <c r="C30" s="84" t="s">
-        <v>39</v>
-      </c>
-      <c r="D30" s="84" t="s">
-        <v>40</v>
-      </c>
-      <c r="E30" s="84" t="s">
-        <v>40</v>
-      </c>
-      <c r="F30" s="81" t="s">
+      <c r="B30" s="77" t="s">
+        <v>38</v>
+      </c>
+      <c r="C30" s="77" t="s">
+        <v>39</v>
+      </c>
+      <c r="D30" s="77" t="s">
+        <v>40</v>
+      </c>
+      <c r="E30" s="77" t="s">
+        <v>40</v>
+      </c>
+      <c r="F30" s="82" t="s">
         <v>70</v>
       </c>
-      <c r="G30" s="82" t="s">
+      <c r="G30" s="83" t="s">
         <v>51</v>
       </c>
-      <c r="H30" s="83">
+      <c r="H30" s="84">
         <f>IF(G30="ILF",'3. 调整因子'!$D$63,IF(G30="EIF",'3. 调整因子'!$D$64,IF(G30="EI",'3. 调整因子'!$D$65,IF(G30="EO",'3. 调整因子'!$D$66,IF(G30="EQ",'3. 调整因子'!$D$67,"")))))</f>
         <v>7</v>
       </c>
@@ -3602,28 +3604,28 @@
       <c r="L30" s="92"/>
     </row>
     <row r="31" s="56" customFormat="1" spans="1:12">
-      <c r="A31" s="79">
+      <c r="A31" s="75">
         <v>23</v>
       </c>
-      <c r="B31" s="84" t="s">
-        <v>38</v>
-      </c>
-      <c r="C31" s="84" t="s">
-        <v>39</v>
-      </c>
-      <c r="D31" s="84" t="s">
-        <v>40</v>
-      </c>
-      <c r="E31" s="84" t="s">
-        <v>40</v>
-      </c>
-      <c r="F31" s="81" t="s">
+      <c r="B31" s="77" t="s">
+        <v>38</v>
+      </c>
+      <c r="C31" s="77" t="s">
+        <v>39</v>
+      </c>
+      <c r="D31" s="77" t="s">
+        <v>40</v>
+      </c>
+      <c r="E31" s="77" t="s">
+        <v>40</v>
+      </c>
+      <c r="F31" s="82" t="s">
         <v>71</v>
       </c>
-      <c r="G31" s="82" t="s">
+      <c r="G31" s="83" t="s">
         <v>51</v>
       </c>
-      <c r="H31" s="83">
+      <c r="H31" s="84">
         <f>IF(G31="ILF",'3. 调整因子'!$D$63,IF(G31="EIF",'3. 调整因子'!$D$64,IF(G31="EI",'3. 调整因子'!$D$65,IF(G31="EO",'3. 调整因子'!$D$66,IF(G31="EQ",'3. 调整因子'!$D$67,"")))))</f>
         <v>7</v>
       </c>
@@ -3640,28 +3642,28 @@
       <c r="L31" s="92"/>
     </row>
     <row r="32" spans="1:12">
-      <c r="A32" s="79">
+      <c r="A32" s="75">
         <v>24</v>
       </c>
-      <c r="B32" s="80" t="s">
-        <v>38</v>
-      </c>
-      <c r="C32" s="80" t="s">
-        <v>39</v>
-      </c>
-      <c r="D32" s="80" t="s">
-        <v>40</v>
-      </c>
-      <c r="E32" s="80" t="s">
+      <c r="B32" s="76" t="s">
+        <v>38</v>
+      </c>
+      <c r="C32" s="76" t="s">
+        <v>39</v>
+      </c>
+      <c r="D32" s="76" t="s">
+        <v>40</v>
+      </c>
+      <c r="E32" s="76" t="s">
         <v>40</v>
       </c>
       <c r="F32" s="85" t="s">
         <v>72</v>
       </c>
-      <c r="G32" s="82" t="s">
+      <c r="G32" s="83" t="s">
         <v>54</v>
       </c>
-      <c r="H32" s="83">
+      <c r="H32" s="84">
         <f>IF(G32="ILF",'3. 调整因子'!$D$63,IF(G32="EIF",'3. 调整因子'!$D$64,IF(G32="EI",'3. 调整因子'!$D$65,IF(G32="EO",'3. 调整因子'!$D$66,IF(G32="EQ",'3. 调整因子'!$D$67,"")))))</f>
         <v>4</v>
       </c>
@@ -3678,28 +3680,28 @@
       <c r="L32" s="90"/>
     </row>
     <row r="33" spans="1:12">
-      <c r="A33" s="79">
+      <c r="A33" s="75">
         <v>25</v>
       </c>
-      <c r="B33" s="80" t="s">
-        <v>38</v>
-      </c>
-      <c r="C33" s="80" t="s">
-        <v>39</v>
-      </c>
-      <c r="D33" s="80" t="s">
-        <v>40</v>
-      </c>
-      <c r="E33" s="80" t="s">
+      <c r="B33" s="76" t="s">
+        <v>38</v>
+      </c>
+      <c r="C33" s="76" t="s">
+        <v>39</v>
+      </c>
+      <c r="D33" s="76" t="s">
+        <v>40</v>
+      </c>
+      <c r="E33" s="76" t="s">
         <v>40</v>
       </c>
       <c r="F33" s="85" t="s">
         <v>73</v>
       </c>
-      <c r="G33" s="82" t="s">
+      <c r="G33" s="83" t="s">
         <v>54</v>
       </c>
-      <c r="H33" s="83">
+      <c r="H33" s="84">
         <f>IF(G33="ILF",'3. 调整因子'!$D$63,IF(G33="EIF",'3. 调整因子'!$D$64,IF(G33="EI",'3. 调整因子'!$D$65,IF(G33="EO",'3. 调整因子'!$D$66,IF(G33="EQ",'3. 调整因子'!$D$67,"")))))</f>
         <v>4</v>
       </c>
@@ -3716,28 +3718,28 @@
       <c r="L33" s="90"/>
     </row>
     <row r="34" spans="1:12">
-      <c r="A34" s="79">
+      <c r="A34" s="75">
         <v>26</v>
       </c>
-      <c r="B34" s="80" t="s">
-        <v>38</v>
-      </c>
-      <c r="C34" s="80" t="s">
-        <v>39</v>
-      </c>
-      <c r="D34" s="80" t="s">
-        <v>40</v>
-      </c>
-      <c r="E34" s="80" t="s">
+      <c r="B34" s="76" t="s">
+        <v>38</v>
+      </c>
+      <c r="C34" s="76" t="s">
+        <v>39</v>
+      </c>
+      <c r="D34" s="76" t="s">
+        <v>40</v>
+      </c>
+      <c r="E34" s="76" t="s">
         <v>40</v>
       </c>
       <c r="F34" s="85" t="s">
         <v>74</v>
       </c>
-      <c r="G34" s="82" t="s">
+      <c r="G34" s="83" t="s">
         <v>54</v>
       </c>
-      <c r="H34" s="83">
+      <c r="H34" s="84">
         <f>IF(G34="ILF",'3. 调整因子'!$D$63,IF(G34="EIF",'3. 调整因子'!$D$64,IF(G34="EI",'3. 调整因子'!$D$65,IF(G34="EO",'3. 调整因子'!$D$66,IF(G34="EQ",'3. 调整因子'!$D$67,"")))))</f>
         <v>4</v>
       </c>
@@ -3754,28 +3756,28 @@
       <c r="L34" s="90"/>
     </row>
     <row r="35" s="56" customFormat="1" spans="1:12">
-      <c r="A35" s="79">
+      <c r="A35" s="75">
         <v>27</v>
       </c>
-      <c r="B35" s="84" t="s">
-        <v>38</v>
-      </c>
-      <c r="C35" s="84" t="s">
-        <v>39</v>
-      </c>
-      <c r="D35" s="84" t="s">
-        <v>40</v>
-      </c>
-      <c r="E35" s="84" t="s">
-        <v>40</v>
-      </c>
-      <c r="F35" s="81" t="s">
+      <c r="B35" s="77" t="s">
+        <v>38</v>
+      </c>
+      <c r="C35" s="77" t="s">
+        <v>39</v>
+      </c>
+      <c r="D35" s="77" t="s">
+        <v>40</v>
+      </c>
+      <c r="E35" s="77" t="s">
+        <v>40</v>
+      </c>
+      <c r="F35" s="82" t="s">
         <v>75</v>
       </c>
-      <c r="G35" s="82" t="s">
+      <c r="G35" s="83" t="s">
         <v>51</v>
       </c>
-      <c r="H35" s="83">
+      <c r="H35" s="84">
         <f>IF(G35="ILF",'3. 调整因子'!$D$63,IF(G35="EIF",'3. 调整因子'!$D$64,IF(G35="EI",'3. 调整因子'!$D$65,IF(G35="EO",'3. 调整因子'!$D$66,IF(G35="EQ",'3. 调整因子'!$D$67,"")))))</f>
         <v>7</v>
       </c>
@@ -3791,28 +3793,28 @@
       <c r="L35" s="92"/>
     </row>
     <row r="36" spans="1:12">
-      <c r="A36" s="79">
+      <c r="A36" s="75">
         <v>28</v>
       </c>
-      <c r="B36" s="80" t="s">
-        <v>38</v>
-      </c>
-      <c r="C36" s="80" t="s">
-        <v>39</v>
-      </c>
-      <c r="D36" s="80" t="s">
-        <v>40</v>
-      </c>
-      <c r="E36" s="80" t="s">
+      <c r="B36" s="76" t="s">
+        <v>38</v>
+      </c>
+      <c r="C36" s="76" t="s">
+        <v>39</v>
+      </c>
+      <c r="D36" s="76" t="s">
+        <v>40</v>
+      </c>
+      <c r="E36" s="76" t="s">
         <v>40</v>
       </c>
       <c r="F36" s="85" t="s">
         <v>76</v>
       </c>
-      <c r="G36" s="82" t="s">
+      <c r="G36" s="83" t="s">
         <v>47</v>
       </c>
-      <c r="H36" s="83">
+      <c r="H36" s="84">
         <f>IF(G36="ILF",'3. 调整因子'!$D$63,IF(G36="EIF",'3. 调整因子'!$D$64,IF(G36="EI",'3. 调整因子'!$D$65,IF(G36="EO",'3. 调整因子'!$D$66,IF(G36="EQ",'3. 调整因子'!$D$67,"")))))</f>
         <v>5</v>
       </c>
@@ -3829,28 +3831,28 @@
       <c r="L36" s="90"/>
     </row>
     <row r="37" spans="1:12">
-      <c r="A37" s="79">
+      <c r="A37" s="75">
         <v>29</v>
       </c>
-      <c r="B37" s="80" t="s">
-        <v>38</v>
-      </c>
-      <c r="C37" s="80" t="s">
-        <v>39</v>
-      </c>
-      <c r="D37" s="80" t="s">
-        <v>40</v>
-      </c>
-      <c r="E37" s="80" t="s">
+      <c r="B37" s="76" t="s">
+        <v>38</v>
+      </c>
+      <c r="C37" s="76" t="s">
+        <v>39</v>
+      </c>
+      <c r="D37" s="76" t="s">
+        <v>40</v>
+      </c>
+      <c r="E37" s="76" t="s">
         <v>40</v>
       </c>
       <c r="F37" s="85" t="s">
         <v>77</v>
       </c>
-      <c r="G37" s="82" t="s">
+      <c r="G37" s="83" t="s">
         <v>54</v>
       </c>
-      <c r="H37" s="83">
+      <c r="H37" s="84">
         <f>IF(G37="ILF",'3. 调整因子'!$D$63,IF(G37="EIF",'3. 调整因子'!$D$64,IF(G37="EI",'3. 调整因子'!$D$65,IF(G37="EO",'3. 调整因子'!$D$66,IF(G37="EQ",'3. 调整因子'!$D$67,"")))))</f>
         <v>4</v>
       </c>
@@ -3867,28 +3869,28 @@
       <c r="L37" s="90"/>
     </row>
     <row r="38" spans="1:12">
-      <c r="A38" s="79">
+      <c r="A38" s="75">
         <v>30</v>
       </c>
-      <c r="B38" s="80" t="s">
-        <v>38</v>
-      </c>
-      <c r="C38" s="80" t="s">
-        <v>39</v>
-      </c>
-      <c r="D38" s="80" t="s">
-        <v>40</v>
-      </c>
-      <c r="E38" s="80" t="s">
+      <c r="B38" s="76" t="s">
+        <v>38</v>
+      </c>
+      <c r="C38" s="76" t="s">
+        <v>39</v>
+      </c>
+      <c r="D38" s="76" t="s">
+        <v>40</v>
+      </c>
+      <c r="E38" s="76" t="s">
         <v>40</v>
       </c>
       <c r="F38" s="85" t="s">
         <v>78</v>
       </c>
-      <c r="G38" s="82" t="s">
+      <c r="G38" s="83" t="s">
         <v>54</v>
       </c>
-      <c r="H38" s="83">
+      <c r="H38" s="84">
         <f>IF(G38="ILF",'3. 调整因子'!$D$63,IF(G38="EIF",'3. 调整因子'!$D$64,IF(G38="EI",'3. 调整因子'!$D$65,IF(G38="EO",'3. 调整因子'!$D$66,IF(G38="EQ",'3. 调整因子'!$D$67,"")))))</f>
         <v>4</v>
       </c>
@@ -3904,28 +3906,28 @@
       <c r="L38" s="90"/>
     </row>
     <row r="39" spans="1:12">
-      <c r="A39" s="79">
+      <c r="A39" s="75">
         <v>31</v>
       </c>
-      <c r="B39" s="80" t="s">
-        <v>38</v>
-      </c>
-      <c r="C39" s="80" t="s">
-        <v>39</v>
-      </c>
-      <c r="D39" s="80" t="s">
-        <v>40</v>
-      </c>
-      <c r="E39" s="80" t="s">
+      <c r="B39" s="76" t="s">
+        <v>38</v>
+      </c>
+      <c r="C39" s="76" t="s">
+        <v>39</v>
+      </c>
+      <c r="D39" s="76" t="s">
+        <v>40</v>
+      </c>
+      <c r="E39" s="76" t="s">
         <v>40</v>
       </c>
       <c r="F39" s="85" t="s">
         <v>79</v>
       </c>
-      <c r="G39" s="82" t="s">
+      <c r="G39" s="83" t="s">
         <v>54</v>
       </c>
-      <c r="H39" s="83">
+      <c r="H39" s="84">
         <f>IF(G39="ILF",'3. 调整因子'!$D$63,IF(G39="EIF",'3. 调整因子'!$D$64,IF(G39="EI",'3. 调整因子'!$D$65,IF(G39="EO",'3. 调整因子'!$D$66,IF(G39="EQ",'3. 调整因子'!$D$67,"")))))</f>
         <v>4</v>
       </c>
@@ -3941,28 +3943,28 @@
       <c r="L39" s="90"/>
     </row>
     <row r="40" spans="1:12">
-      <c r="A40" s="79">
+      <c r="A40" s="75">
         <v>32</v>
       </c>
-      <c r="B40" s="80" t="s">
-        <v>38</v>
-      </c>
-      <c r="C40" s="80" t="s">
-        <v>39</v>
-      </c>
-      <c r="D40" s="80" t="s">
-        <v>40</v>
-      </c>
-      <c r="E40" s="80" t="s">
+      <c r="B40" s="76" t="s">
+        <v>38</v>
+      </c>
+      <c r="C40" s="76" t="s">
+        <v>39</v>
+      </c>
+      <c r="D40" s="76" t="s">
+        <v>40</v>
+      </c>
+      <c r="E40" s="76" t="s">
         <v>40</v>
       </c>
       <c r="F40" s="85" t="s">
         <v>80</v>
       </c>
-      <c r="G40" s="82" t="s">
+      <c r="G40" s="83" t="s">
         <v>54</v>
       </c>
-      <c r="H40" s="83">
+      <c r="H40" s="84">
         <f>IF(G40="ILF",'3. 调整因子'!$D$63,IF(G40="EIF",'3. 调整因子'!$D$64,IF(G40="EI",'3. 调整因子'!$D$65,IF(G40="EO",'3. 调整因子'!$D$66,IF(G40="EQ",'3. 调整因子'!$D$67,"")))))</f>
         <v>4</v>
       </c>
@@ -3978,28 +3980,28 @@
       <c r="L40" s="90"/>
     </row>
     <row r="41" s="56" customFormat="1" spans="1:12">
-      <c r="A41" s="79">
+      <c r="A41" s="75">
         <v>33</v>
       </c>
-      <c r="B41" s="84" t="s">
-        <v>38</v>
-      </c>
-      <c r="C41" s="84" t="s">
-        <v>39</v>
-      </c>
-      <c r="D41" s="84" t="s">
-        <v>40</v>
-      </c>
-      <c r="E41" s="84" t="s">
-        <v>40</v>
-      </c>
-      <c r="F41" s="81" t="s">
+      <c r="B41" s="77" t="s">
+        <v>38</v>
+      </c>
+      <c r="C41" s="77" t="s">
+        <v>39</v>
+      </c>
+      <c r="D41" s="77" t="s">
+        <v>40</v>
+      </c>
+      <c r="E41" s="77" t="s">
+        <v>40</v>
+      </c>
+      <c r="F41" s="82" t="s">
         <v>81</v>
       </c>
-      <c r="G41" s="82" t="s">
+      <c r="G41" s="83" t="s">
         <v>51</v>
       </c>
-      <c r="H41" s="83">
+      <c r="H41" s="84">
         <f>IF(G41="ILF",'3. 调整因子'!$D$63,IF(G41="EIF",'3. 调整因子'!$D$64,IF(G41="EI",'3. 调整因子'!$D$65,IF(G41="EO",'3. 调整因子'!$D$66,IF(G41="EQ",'3. 调整因子'!$D$67,"")))))</f>
         <v>7</v>
       </c>
@@ -4016,28 +4018,28 @@
       <c r="L41" s="92"/>
     </row>
     <row r="42" s="56" customFormat="1" spans="1:12">
-      <c r="A42" s="79">
+      <c r="A42" s="75">
         <v>34</v>
       </c>
-      <c r="B42" s="84" t="s">
-        <v>38</v>
-      </c>
-      <c r="C42" s="84" t="s">
-        <v>39</v>
-      </c>
-      <c r="D42" s="84" t="s">
-        <v>40</v>
-      </c>
-      <c r="E42" s="84" t="s">
-        <v>40</v>
-      </c>
-      <c r="F42" s="81" t="s">
+      <c r="B42" s="77" t="s">
+        <v>38</v>
+      </c>
+      <c r="C42" s="77" t="s">
+        <v>39</v>
+      </c>
+      <c r="D42" s="77" t="s">
+        <v>40</v>
+      </c>
+      <c r="E42" s="77" t="s">
+        <v>40</v>
+      </c>
+      <c r="F42" s="82" t="s">
         <v>82</v>
       </c>
-      <c r="G42" s="82" t="s">
+      <c r="G42" s="83" t="s">
         <v>51</v>
       </c>
-      <c r="H42" s="83">
+      <c r="H42" s="84">
         <f>IF(G42="ILF",'3. 调整因子'!$D$63,IF(G42="EIF",'3. 调整因子'!$D$64,IF(G42="EI",'3. 调整因子'!$D$65,IF(G42="EO",'3. 调整因子'!$D$66,IF(G42="EQ",'3. 调整因子'!$D$67,"")))))</f>
         <v>7</v>
       </c>
@@ -4054,28 +4056,28 @@
       <c r="L42" s="92"/>
     </row>
     <row r="43" spans="1:12">
-      <c r="A43" s="79">
+      <c r="A43" s="75">
         <v>35</v>
       </c>
-      <c r="B43" s="80" t="s">
-        <v>38</v>
-      </c>
-      <c r="C43" s="80" t="s">
-        <v>39</v>
-      </c>
-      <c r="D43" s="80" t="s">
-        <v>40</v>
-      </c>
-      <c r="E43" s="80" t="s">
+      <c r="B43" s="76" t="s">
+        <v>38</v>
+      </c>
+      <c r="C43" s="76" t="s">
+        <v>39</v>
+      </c>
+      <c r="D43" s="76" t="s">
+        <v>40</v>
+      </c>
+      <c r="E43" s="76" t="s">
         <v>40</v>
       </c>
       <c r="F43" s="85" t="s">
         <v>83</v>
       </c>
-      <c r="G43" s="82" t="s">
+      <c r="G43" s="83" t="s">
         <v>47</v>
       </c>
-      <c r="H43" s="83">
+      <c r="H43" s="84">
         <f>IF(G43="ILF",'3. 调整因子'!$D$63,IF(G43="EIF",'3. 调整因子'!$D$64,IF(G43="EI",'3. 调整因子'!$D$65,IF(G43="EO",'3. 调整因子'!$D$66,IF(G43="EQ",'3. 调整因子'!$D$67,"")))))</f>
         <v>5</v>
       </c>
@@ -4092,28 +4094,28 @@
       <c r="L43" s="90"/>
     </row>
     <row r="44" s="56" customFormat="1" spans="1:12">
-      <c r="A44" s="79">
+      <c r="A44" s="75">
         <v>36</v>
       </c>
-      <c r="B44" s="84" t="s">
-        <v>38</v>
-      </c>
-      <c r="C44" s="84" t="s">
-        <v>39</v>
-      </c>
-      <c r="D44" s="84" t="s">
-        <v>40</v>
-      </c>
-      <c r="E44" s="84" t="s">
-        <v>40</v>
-      </c>
-      <c r="F44" s="81" t="s">
+      <c r="B44" s="77" t="s">
+        <v>38</v>
+      </c>
+      <c r="C44" s="77" t="s">
+        <v>39</v>
+      </c>
+      <c r="D44" s="77" t="s">
+        <v>40</v>
+      </c>
+      <c r="E44" s="77" t="s">
+        <v>40</v>
+      </c>
+      <c r="F44" s="82" t="s">
         <v>84</v>
       </c>
-      <c r="G44" s="82" t="s">
+      <c r="G44" s="83" t="s">
         <v>51</v>
       </c>
-      <c r="H44" s="83">
+      <c r="H44" s="84">
         <f>IF(G44="ILF",'3. 调整因子'!$D$63,IF(G44="EIF",'3. 调整因子'!$D$64,IF(G44="EI",'3. 调整因子'!$D$65,IF(G44="EO",'3. 调整因子'!$D$66,IF(G44="EQ",'3. 调整因子'!$D$67,"")))))</f>
         <v>7</v>
       </c>
@@ -4130,28 +4132,28 @@
       <c r="L44" s="92"/>
     </row>
     <row r="45" spans="1:12">
-      <c r="A45" s="79">
+      <c r="A45" s="75">
         <v>37</v>
       </c>
-      <c r="B45" s="80" t="s">
-        <v>38</v>
-      </c>
-      <c r="C45" s="80" t="s">
-        <v>39</v>
-      </c>
-      <c r="D45" s="80" t="s">
-        <v>40</v>
-      </c>
-      <c r="E45" s="80" t="s">
+      <c r="B45" s="76" t="s">
+        <v>38</v>
+      </c>
+      <c r="C45" s="76" t="s">
+        <v>39</v>
+      </c>
+      <c r="D45" s="76" t="s">
+        <v>40</v>
+      </c>
+      <c r="E45" s="76" t="s">
         <v>40</v>
       </c>
       <c r="F45" s="85" t="s">
         <v>85</v>
       </c>
-      <c r="G45" s="82" t="s">
+      <c r="G45" s="83" t="s">
         <v>47</v>
       </c>
-      <c r="H45" s="83">
+      <c r="H45" s="84">
         <f>IF(G45="ILF",'3. 调整因子'!$D$63,IF(G45="EIF",'3. 调整因子'!$D$64,IF(G45="EI",'3. 调整因子'!$D$65,IF(G45="EO",'3. 调整因子'!$D$66,IF(G45="EQ",'3. 调整因子'!$D$67,"")))))</f>
         <v>5</v>
       </c>
@@ -4168,28 +4170,28 @@
       <c r="L45" s="90"/>
     </row>
     <row r="46" spans="1:12">
-      <c r="A46" s="79">
-        <v>38</v>
-      </c>
-      <c r="B46" s="80" t="s">
-        <v>38</v>
-      </c>
-      <c r="C46" s="80" t="s">
-        <v>39</v>
-      </c>
-      <c r="D46" s="80" t="s">
-        <v>40</v>
-      </c>
-      <c r="E46" s="80" t="s">
+      <c r="A46" s="75">
+        <v>38</v>
+      </c>
+      <c r="B46" s="76" t="s">
+        <v>38</v>
+      </c>
+      <c r="C46" s="76" t="s">
+        <v>39</v>
+      </c>
+      <c r="D46" s="76" t="s">
+        <v>40</v>
+      </c>
+      <c r="E46" s="76" t="s">
         <v>40</v>
       </c>
       <c r="F46" s="85" t="s">
         <v>86</v>
       </c>
-      <c r="G46" s="82" t="s">
+      <c r="G46" s="83" t="s">
         <v>47</v>
       </c>
-      <c r="H46" s="83">
+      <c r="H46" s="84">
         <f>IF(G46="ILF",'3. 调整因子'!$D$63,IF(G46="EIF",'3. 调整因子'!$D$64,IF(G46="EI",'3. 调整因子'!$D$65,IF(G46="EO",'3. 调整因子'!$D$66,IF(G46="EQ",'3. 调整因子'!$D$67,"")))))</f>
         <v>5</v>
       </c>
@@ -4206,28 +4208,28 @@
       <c r="L46" s="90"/>
     </row>
     <row r="47" spans="1:12">
-      <c r="A47" s="79">
-        <v>39</v>
-      </c>
-      <c r="B47" s="80" t="s">
-        <v>38</v>
-      </c>
-      <c r="C47" s="80" t="s">
-        <v>39</v>
-      </c>
-      <c r="D47" s="80" t="s">
-        <v>40</v>
-      </c>
-      <c r="E47" s="80" t="s">
+      <c r="A47" s="75">
+        <v>39</v>
+      </c>
+      <c r="B47" s="76" t="s">
+        <v>38</v>
+      </c>
+      <c r="C47" s="76" t="s">
+        <v>39</v>
+      </c>
+      <c r="D47" s="76" t="s">
+        <v>40</v>
+      </c>
+      <c r="E47" s="76" t="s">
         <v>40</v>
       </c>
       <c r="F47" s="85" t="s">
         <v>87</v>
       </c>
-      <c r="G47" s="82" t="s">
+      <c r="G47" s="83" t="s">
         <v>47</v>
       </c>
-      <c r="H47" s="83">
+      <c r="H47" s="84">
         <f>IF(G47="ILF",'3. 调整因子'!$D$63,IF(G47="EIF",'3. 调整因子'!$D$64,IF(G47="EI",'3. 调整因子'!$D$65,IF(G47="EO",'3. 调整因子'!$D$66,IF(G47="EQ",'3. 调整因子'!$D$67,"")))))</f>
         <v>5</v>
       </c>
@@ -4244,28 +4246,28 @@
       <c r="L47" s="90"/>
     </row>
     <row r="48" spans="1:12">
-      <c r="A48" s="79">
-        <v>40</v>
-      </c>
-      <c r="B48" s="80" t="s">
-        <v>38</v>
-      </c>
-      <c r="C48" s="80" t="s">
-        <v>39</v>
-      </c>
-      <c r="D48" s="80" t="s">
-        <v>40</v>
-      </c>
-      <c r="E48" s="80" t="s">
+      <c r="A48" s="75">
+        <v>40</v>
+      </c>
+      <c r="B48" s="76" t="s">
+        <v>38</v>
+      </c>
+      <c r="C48" s="76" t="s">
+        <v>39</v>
+      </c>
+      <c r="D48" s="76" t="s">
+        <v>40</v>
+      </c>
+      <c r="E48" s="76" t="s">
         <v>40</v>
       </c>
       <c r="F48" s="85" t="s">
         <v>88</v>
       </c>
-      <c r="G48" s="82" t="s">
+      <c r="G48" s="83" t="s">
         <v>47</v>
       </c>
-      <c r="H48" s="83">
+      <c r="H48" s="84">
         <f>IF(G48="ILF",'3. 调整因子'!$D$63,IF(G48="EIF",'3. 调整因子'!$D$64,IF(G48="EI",'3. 调整因子'!$D$65,IF(G48="EO",'3. 调整因子'!$D$66,IF(G48="EQ",'3. 调整因子'!$D$67,"")))))</f>
         <v>5</v>
       </c>
@@ -4282,28 +4284,28 @@
       <c r="L48" s="90"/>
     </row>
     <row r="49" s="58" customFormat="1" spans="1:12">
-      <c r="A49" s="79">
+      <c r="A49" s="75">
         <v>41</v>
       </c>
-      <c r="B49" s="84" t="s">
-        <v>38</v>
-      </c>
-      <c r="C49" s="84" t="s">
-        <v>39</v>
-      </c>
-      <c r="D49" s="84" t="s">
-        <v>40</v>
-      </c>
-      <c r="E49" s="84" t="s">
+      <c r="B49" s="77" t="s">
+        <v>38</v>
+      </c>
+      <c r="C49" s="77" t="s">
+        <v>39</v>
+      </c>
+      <c r="D49" s="77" t="s">
+        <v>40</v>
+      </c>
+      <c r="E49" s="77" t="s">
         <v>40</v>
       </c>
       <c r="F49" s="86" t="s">
         <v>89</v>
       </c>
-      <c r="G49" s="82" t="s">
+      <c r="G49" s="83" t="s">
         <v>51</v>
       </c>
-      <c r="H49" s="83">
+      <c r="H49" s="84">
         <f>IF(G49="ILF",'3. 调整因子'!$D$63,IF(G49="EIF",'3. 调整因子'!$D$64,IF(G49="EI",'3. 调整因子'!$D$65,IF(G49="EO",'3. 调整因子'!$D$66,IF(G49="EQ",'3. 调整因子'!$D$67,"")))))</f>
         <v>7</v>
       </c>
@@ -4319,28 +4321,28 @@
       <c r="L49" s="92"/>
     </row>
     <row r="50" spans="1:12">
-      <c r="A50" s="79">
+      <c r="A50" s="75">
         <v>42</v>
       </c>
-      <c r="B50" s="80" t="s">
-        <v>38</v>
-      </c>
-      <c r="C50" s="80" t="s">
-        <v>39</v>
-      </c>
-      <c r="D50" s="80" t="s">
-        <v>40</v>
-      </c>
-      <c r="E50" s="80" t="s">
+      <c r="B50" s="76" t="s">
+        <v>38</v>
+      </c>
+      <c r="C50" s="76" t="s">
+        <v>39</v>
+      </c>
+      <c r="D50" s="76" t="s">
+        <v>40</v>
+      </c>
+      <c r="E50" s="76" t="s">
         <v>40</v>
       </c>
       <c r="F50" s="85" t="s">
         <v>90</v>
       </c>
-      <c r="G50" s="82" t="s">
+      <c r="G50" s="83" t="s">
         <v>47</v>
       </c>
-      <c r="H50" s="83">
+      <c r="H50" s="84">
         <f>IF(G50="ILF",'3. 调整因子'!$D$63,IF(G50="EIF",'3. 调整因子'!$D$64,IF(G50="EI",'3. 调整因子'!$D$65,IF(G50="EO",'3. 调整因子'!$D$66,IF(G50="EQ",'3. 调整因子'!$D$67,"")))))</f>
         <v>5</v>
       </c>
@@ -4357,28 +4359,28 @@
       <c r="L50" s="90"/>
     </row>
     <row r="51" customFormat="1" spans="1:12">
-      <c r="A51" s="79">
-        <v>43</v>
-      </c>
-      <c r="B51" s="80" t="s">
-        <v>38</v>
-      </c>
-      <c r="C51" s="80" t="s">
-        <v>39</v>
-      </c>
-      <c r="D51" s="80" t="s">
-        <v>40</v>
-      </c>
-      <c r="E51" s="80" t="s">
+      <c r="A51" s="75">
+        <v>43</v>
+      </c>
+      <c r="B51" s="76" t="s">
+        <v>38</v>
+      </c>
+      <c r="C51" s="76" t="s">
+        <v>39</v>
+      </c>
+      <c r="D51" s="76" t="s">
+        <v>40</v>
+      </c>
+      <c r="E51" s="76" t="s">
         <v>40</v>
       </c>
       <c r="F51" s="85" t="s">
         <v>91</v>
       </c>
-      <c r="G51" s="82" t="s">
+      <c r="G51" s="83" t="s">
         <v>47</v>
       </c>
-      <c r="H51" s="83">
+      <c r="H51" s="84">
         <f>IF(G51="ILF",'3. 调整因子'!$D$63,IF(G51="EIF",'3. 调整因子'!$D$64,IF(G51="EI",'3. 调整因子'!$D$65,IF(G51="EO",'3. 调整因子'!$D$66,IF(G51="EQ",'3. 调整因子'!$D$67,"")))))</f>
         <v>5</v>
       </c>
@@ -4395,28 +4397,28 @@
       <c r="L51" s="90"/>
     </row>
     <row r="52" s="58" customFormat="1" spans="1:12">
-      <c r="A52" s="79">
-        <v>44</v>
-      </c>
-      <c r="B52" s="84" t="s">
-        <v>38</v>
-      </c>
-      <c r="C52" s="84" t="s">
-        <v>39</v>
-      </c>
-      <c r="D52" s="84" t="s">
-        <v>40</v>
-      </c>
-      <c r="E52" s="84" t="s">
+      <c r="A52" s="75">
+        <v>44</v>
+      </c>
+      <c r="B52" s="77" t="s">
+        <v>38</v>
+      </c>
+      <c r="C52" s="77" t="s">
+        <v>39</v>
+      </c>
+      <c r="D52" s="77" t="s">
+        <v>40</v>
+      </c>
+      <c r="E52" s="77" t="s">
         <v>40</v>
       </c>
       <c r="F52" s="86" t="s">
         <v>92</v>
       </c>
-      <c r="G52" s="82" t="s">
+      <c r="G52" s="83" t="s">
         <v>51</v>
       </c>
-      <c r="H52" s="83">
+      <c r="H52" s="84">
         <f>IF(G52="ILF",'3. 调整因子'!$D$63,IF(G52="EIF",'3. 调整因子'!$D$64,IF(G52="EI",'3. 调整因子'!$D$65,IF(G52="EO",'3. 调整因子'!$D$66,IF(G52="EQ",'3. 调整因子'!$D$67,"")))))</f>
         <v>7</v>
       </c>
@@ -4432,28 +4434,28 @@
       <c r="L52" s="92"/>
     </row>
     <row r="53" s="58" customFormat="1" spans="1:12">
-      <c r="A53" s="79">
+      <c r="A53" s="75">
         <v>45</v>
       </c>
-      <c r="B53" s="84" t="s">
-        <v>38</v>
-      </c>
-      <c r="C53" s="84" t="s">
-        <v>39</v>
-      </c>
-      <c r="D53" s="84" t="s">
-        <v>40</v>
-      </c>
-      <c r="E53" s="84" t="s">
+      <c r="B53" s="77" t="s">
+        <v>38</v>
+      </c>
+      <c r="C53" s="77" t="s">
+        <v>39</v>
+      </c>
+      <c r="D53" s="77" t="s">
+        <v>40</v>
+      </c>
+      <c r="E53" s="77" t="s">
         <v>40</v>
       </c>
       <c r="F53" s="86" t="s">
         <v>93</v>
       </c>
-      <c r="G53" s="82" t="s">
+      <c r="G53" s="83" t="s">
         <v>51</v>
       </c>
-      <c r="H53" s="83">
+      <c r="H53" s="84">
         <f>IF(G53="ILF",'3. 调整因子'!$D$63,IF(G53="EIF",'3. 调整因子'!$D$64,IF(G53="EI",'3. 调整因子'!$D$65,IF(G53="EO",'3. 调整因子'!$D$66,IF(G53="EQ",'3. 调整因子'!$D$67,"")))))</f>
         <v>7</v>
       </c>
@@ -4470,28 +4472,28 @@
       <c r="L53" s="92"/>
     </row>
     <row r="54" s="57" customFormat="1" spans="1:12">
-      <c r="A54" s="79">
+      <c r="A54" s="75">
         <v>46</v>
       </c>
-      <c r="B54" s="80" t="s">
-        <v>38</v>
-      </c>
-      <c r="C54" s="80" t="s">
-        <v>39</v>
-      </c>
-      <c r="D54" s="80" t="s">
-        <v>40</v>
-      </c>
-      <c r="E54" s="80" t="s">
+      <c r="B54" s="76" t="s">
+        <v>38</v>
+      </c>
+      <c r="C54" s="76" t="s">
+        <v>39</v>
+      </c>
+      <c r="D54" s="76" t="s">
+        <v>40</v>
+      </c>
+      <c r="E54" s="76" t="s">
         <v>40</v>
       </c>
       <c r="F54" s="85" t="s">
         <v>94</v>
       </c>
-      <c r="G54" s="82" t="s">
+      <c r="G54" s="83" t="s">
         <v>47</v>
       </c>
-      <c r="H54" s="83">
+      <c r="H54" s="84">
         <f>IF(G54="ILF",'3. 调整因子'!$D$63,IF(G54="EIF",'3. 调整因子'!$D$64,IF(G54="EI",'3. 调整因子'!$D$65,IF(G54="EO",'3. 调整因子'!$D$66,IF(G54="EQ",'3. 调整因子'!$D$67,"")))))</f>
         <v>5</v>
       </c>
@@ -4508,28 +4510,28 @@
       <c r="L54" s="90"/>
     </row>
     <row r="55" s="57" customFormat="1" spans="1:12">
-      <c r="A55" s="79">
+      <c r="A55" s="75">
         <v>47</v>
       </c>
-      <c r="B55" s="80" t="s">
-        <v>38</v>
-      </c>
-      <c r="C55" s="80" t="s">
-        <v>39</v>
-      </c>
-      <c r="D55" s="80" t="s">
-        <v>40</v>
-      </c>
-      <c r="E55" s="80" t="s">
+      <c r="B55" s="76" t="s">
+        <v>38</v>
+      </c>
+      <c r="C55" s="76" t="s">
+        <v>39</v>
+      </c>
+      <c r="D55" s="76" t="s">
+        <v>40</v>
+      </c>
+      <c r="E55" s="76" t="s">
         <v>40</v>
       </c>
       <c r="F55" s="85" t="s">
         <v>95</v>
       </c>
-      <c r="G55" s="82" t="s">
+      <c r="G55" s="83" t="s">
         <v>47</v>
       </c>
-      <c r="H55" s="83">
+      <c r="H55" s="84">
         <f>IF(G55="ILF",'3. 调整因子'!$D$63,IF(G55="EIF",'3. 调整因子'!$D$64,IF(G55="EI",'3. 调整因子'!$D$65,IF(G55="EO",'3. 调整因子'!$D$66,IF(G55="EQ",'3. 调整因子'!$D$67,"")))))</f>
         <v>5</v>
       </c>
@@ -4546,28 +4548,28 @@
       <c r="L55" s="90"/>
     </row>
     <row r="56" s="58" customFormat="1" spans="1:12">
-      <c r="A56" s="79">
+      <c r="A56" s="75">
         <v>48</v>
       </c>
-      <c r="B56" s="84" t="s">
-        <v>38</v>
-      </c>
-      <c r="C56" s="84" t="s">
-        <v>39</v>
-      </c>
-      <c r="D56" s="84" t="s">
-        <v>40</v>
-      </c>
-      <c r="E56" s="84" t="s">
+      <c r="B56" s="77" t="s">
+        <v>38</v>
+      </c>
+      <c r="C56" s="77" t="s">
+        <v>39</v>
+      </c>
+      <c r="D56" s="77" t="s">
+        <v>40</v>
+      </c>
+      <c r="E56" s="77" t="s">
         <v>40</v>
       </c>
       <c r="F56" s="86" t="s">
         <v>96</v>
       </c>
-      <c r="G56" s="82" t="s">
+      <c r="G56" s="83" t="s">
         <v>51</v>
       </c>
-      <c r="H56" s="83">
+      <c r="H56" s="84">
         <f>IF(G56="ILF",'3. 调整因子'!$D$63,IF(G56="EIF",'3. 调整因子'!$D$64,IF(G56="EI",'3. 调整因子'!$D$65,IF(G56="EO",'3. 调整因子'!$D$66,IF(G56="EQ",'3. 调整因子'!$D$67,"")))))</f>
         <v>7</v>
       </c>
@@ -4584,28 +4586,28 @@
       <c r="L56" s="92"/>
     </row>
     <row r="57" s="57" customFormat="1" spans="1:12">
-      <c r="A57" s="79">
+      <c r="A57" s="75">
         <v>49</v>
       </c>
-      <c r="B57" s="80" t="s">
-        <v>38</v>
-      </c>
-      <c r="C57" s="80" t="s">
-        <v>39</v>
-      </c>
-      <c r="D57" s="80" t="s">
-        <v>40</v>
-      </c>
-      <c r="E57" s="80" t="s">
-        <v>40</v>
-      </c>
-      <c r="F57" s="81" t="s">
+      <c r="B57" s="76" t="s">
+        <v>38</v>
+      </c>
+      <c r="C57" s="76" t="s">
+        <v>39</v>
+      </c>
+      <c r="D57" s="76" t="s">
+        <v>40</v>
+      </c>
+      <c r="E57" s="76" t="s">
+        <v>40</v>
+      </c>
+      <c r="F57" s="82" t="s">
         <v>97</v>
       </c>
-      <c r="G57" s="82" t="s">
+      <c r="G57" s="83" t="s">
         <v>47</v>
       </c>
-      <c r="H57" s="83">
+      <c r="H57" s="84">
         <f>IF(G57="ILF",'3. 调整因子'!$D$63,IF(G57="EIF",'3. 调整因子'!$D$64,IF(G57="EI",'3. 调整因子'!$D$65,IF(G57="EO",'3. 调整因子'!$D$66,IF(G57="EQ",'3. 调整因子'!$D$67,"")))))</f>
         <v>5</v>
       </c>
@@ -4622,28 +4624,28 @@
       <c r="L57" s="90"/>
     </row>
     <row r="58" s="58" customFormat="1" spans="1:12">
-      <c r="A58" s="79">
+      <c r="A58" s="75">
         <v>50</v>
       </c>
-      <c r="B58" s="84" t="s">
-        <v>38</v>
-      </c>
-      <c r="C58" s="84" t="s">
-        <v>39</v>
-      </c>
-      <c r="D58" s="84" t="s">
-        <v>40</v>
-      </c>
-      <c r="E58" s="84" t="s">
+      <c r="B58" s="77" t="s">
+        <v>38</v>
+      </c>
+      <c r="C58" s="77" t="s">
+        <v>39</v>
+      </c>
+      <c r="D58" s="77" t="s">
+        <v>40</v>
+      </c>
+      <c r="E58" s="77" t="s">
         <v>40</v>
       </c>
       <c r="F58" s="86" t="s">
         <v>98</v>
       </c>
-      <c r="G58" s="82" t="s">
+      <c r="G58" s="83" t="s">
         <v>47</v>
       </c>
-      <c r="H58" s="83">
+      <c r="H58" s="84">
         <f>IF(G58="ILF",'3. 调整因子'!$D$63,IF(G58="EIF",'3. 调整因子'!$D$64,IF(G58="EI",'3. 调整因子'!$D$65,IF(G58="EO",'3. 调整因子'!$D$66,IF(G58="EQ",'3. 调整因子'!$D$67,"")))))</f>
         <v>5</v>
       </c>
@@ -4659,28 +4661,28 @@
       <c r="L58" s="92"/>
     </row>
     <row r="59" s="57" customFormat="1" spans="1:12">
-      <c r="A59" s="79">
+      <c r="A59" s="75">
         <v>51</v>
       </c>
-      <c r="B59" s="80" t="s">
-        <v>38</v>
-      </c>
-      <c r="C59" s="80" t="s">
-        <v>39</v>
-      </c>
-      <c r="D59" s="80" t="s">
-        <v>40</v>
-      </c>
-      <c r="E59" s="80" t="s">
+      <c r="B59" s="76" t="s">
+        <v>38</v>
+      </c>
+      <c r="C59" s="76" t="s">
+        <v>39</v>
+      </c>
+      <c r="D59" s="76" t="s">
+        <v>40</v>
+      </c>
+      <c r="E59" s="76" t="s">
         <v>40</v>
       </c>
       <c r="F59" s="85" t="s">
         <v>99</v>
       </c>
-      <c r="G59" s="82" t="s">
+      <c r="G59" s="83" t="s">
         <v>47</v>
       </c>
-      <c r="H59" s="83">
+      <c r="H59" s="84">
         <f>IF(G59="ILF",'3. 调整因子'!$D$63,IF(G59="EIF",'3. 调整因子'!$D$64,IF(G59="EI",'3. 调整因子'!$D$65,IF(G59="EO",'3. 调整因子'!$D$66,IF(G59="EQ",'3. 调整因子'!$D$67,"")))))</f>
         <v>5</v>
       </c>
@@ -4697,28 +4699,28 @@
       <c r="L59" s="90"/>
     </row>
     <row r="60" s="57" customFormat="1" spans="1:12">
-      <c r="A60" s="79">
+      <c r="A60" s="75">
         <v>52</v>
       </c>
-      <c r="B60" s="80" t="s">
-        <v>38</v>
-      </c>
-      <c r="C60" s="80" t="s">
-        <v>39</v>
-      </c>
-      <c r="D60" s="80" t="s">
-        <v>40</v>
-      </c>
-      <c r="E60" s="80" t="s">
+      <c r="B60" s="76" t="s">
+        <v>38</v>
+      </c>
+      <c r="C60" s="76" t="s">
+        <v>39</v>
+      </c>
+      <c r="D60" s="76" t="s">
+        <v>40</v>
+      </c>
+      <c r="E60" s="76" t="s">
         <v>40</v>
       </c>
       <c r="F60" s="85" t="s">
         <v>100</v>
       </c>
-      <c r="G60" s="82" t="s">
+      <c r="G60" s="83" t="s">
         <v>47</v>
       </c>
-      <c r="H60" s="83">
+      <c r="H60" s="84">
         <f>IF(G60="ILF",'3. 调整因子'!$D$63,IF(G60="EIF",'3. 调整因子'!$D$64,IF(G60="EI",'3. 调整因子'!$D$65,IF(G60="EO",'3. 调整因子'!$D$66,IF(G60="EQ",'3. 调整因子'!$D$67,"")))))</f>
         <v>5</v>
       </c>
@@ -4735,28 +4737,28 @@
       <c r="L60" s="90"/>
     </row>
     <row r="61" s="57" customFormat="1" spans="1:12">
-      <c r="A61" s="79">
+      <c r="A61" s="75">
         <v>53</v>
       </c>
-      <c r="B61" s="80" t="s">
-        <v>38</v>
-      </c>
-      <c r="C61" s="80" t="s">
-        <v>39</v>
-      </c>
-      <c r="D61" s="80" t="s">
-        <v>40</v>
-      </c>
-      <c r="E61" s="80" t="s">
+      <c r="B61" s="76" t="s">
+        <v>38</v>
+      </c>
+      <c r="C61" s="76" t="s">
+        <v>39</v>
+      </c>
+      <c r="D61" s="76" t="s">
+        <v>40</v>
+      </c>
+      <c r="E61" s="76" t="s">
         <v>40</v>
       </c>
       <c r="F61" s="85" t="s">
         <v>101</v>
       </c>
-      <c r="G61" s="82" t="s">
+      <c r="G61" s="83" t="s">
         <v>47</v>
       </c>
-      <c r="H61" s="83">
+      <c r="H61" s="84">
         <f>IF(G61="ILF",'3. 调整因子'!$D$63,IF(G61="EIF",'3. 调整因子'!$D$64,IF(G61="EI",'3. 调整因子'!$D$65,IF(G61="EO",'3. 调整因子'!$D$66,IF(G61="EQ",'3. 调整因子'!$D$67,"")))))</f>
         <v>5</v>
       </c>
@@ -4773,28 +4775,28 @@
       <c r="L61" s="90"/>
     </row>
     <row r="62" s="57" customFormat="1" spans="1:12">
-      <c r="A62" s="79">
+      <c r="A62" s="75">
         <v>54</v>
       </c>
-      <c r="B62" s="80" t="s">
-        <v>38</v>
-      </c>
-      <c r="C62" s="80" t="s">
-        <v>39</v>
-      </c>
-      <c r="D62" s="80" t="s">
-        <v>40</v>
-      </c>
-      <c r="E62" s="80" t="s">
+      <c r="B62" s="76" t="s">
+        <v>38</v>
+      </c>
+      <c r="C62" s="76" t="s">
+        <v>39</v>
+      </c>
+      <c r="D62" s="76" t="s">
+        <v>40</v>
+      </c>
+      <c r="E62" s="76" t="s">
         <v>40</v>
       </c>
       <c r="F62" s="85" t="s">
         <v>102</v>
       </c>
-      <c r="G62" s="82" t="s">
+      <c r="G62" s="83" t="s">
         <v>47</v>
       </c>
-      <c r="H62" s="83">
+      <c r="H62" s="84">
         <f>IF(G62="ILF",'3. 调整因子'!$D$63,IF(G62="EIF",'3. 调整因子'!$D$64,IF(G62="EI",'3. 调整因子'!$D$65,IF(G62="EO",'3. 调整因子'!$D$66,IF(G62="EQ",'3. 调整因子'!$D$67,"")))))</f>
         <v>5</v>
       </c>
@@ -4811,28 +4813,28 @@
       <c r="L62" s="90"/>
     </row>
     <row r="63" s="57" customFormat="1" spans="1:12">
-      <c r="A63" s="79">
+      <c r="A63" s="75">
         <v>55</v>
       </c>
-      <c r="B63" s="80" t="s">
-        <v>38</v>
-      </c>
-      <c r="C63" s="80" t="s">
-        <v>39</v>
-      </c>
-      <c r="D63" s="80" t="s">
-        <v>40</v>
-      </c>
-      <c r="E63" s="80" t="s">
+      <c r="B63" s="76" t="s">
+        <v>38</v>
+      </c>
+      <c r="C63" s="76" t="s">
+        <v>39</v>
+      </c>
+      <c r="D63" s="76" t="s">
+        <v>40</v>
+      </c>
+      <c r="E63" s="76" t="s">
         <v>40</v>
       </c>
       <c r="F63" s="85" t="s">
         <v>103</v>
       </c>
-      <c r="G63" s="82" t="s">
+      <c r="G63" s="83" t="s">
         <v>47</v>
       </c>
-      <c r="H63" s="83">
+      <c r="H63" s="84">
         <f>IF(G63="ILF",'3. 调整因子'!$D$63,IF(G63="EIF",'3. 调整因子'!$D$64,IF(G63="EI",'3. 调整因子'!$D$65,IF(G63="EO",'3. 调整因子'!$D$66,IF(G63="EQ",'3. 调整因子'!$D$67,"")))))</f>
         <v>5</v>
       </c>
@@ -4848,28 +4850,28 @@
       <c r="L63" s="90"/>
     </row>
     <row r="64" s="57" customFormat="1" spans="1:12">
-      <c r="A64" s="79">
+      <c r="A64" s="75">
         <v>56</v>
       </c>
-      <c r="B64" s="80" t="s">
-        <v>38</v>
-      </c>
-      <c r="C64" s="80" t="s">
-        <v>39</v>
-      </c>
-      <c r="D64" s="80" t="s">
-        <v>40</v>
-      </c>
-      <c r="E64" s="80" t="s">
+      <c r="B64" s="76" t="s">
+        <v>38</v>
+      </c>
+      <c r="C64" s="76" t="s">
+        <v>39</v>
+      </c>
+      <c r="D64" s="76" t="s">
+        <v>40</v>
+      </c>
+      <c r="E64" s="76" t="s">
         <v>40</v>
       </c>
       <c r="F64" s="85" t="s">
         <v>104</v>
       </c>
-      <c r="G64" s="82" t="s">
+      <c r="G64" s="83" t="s">
         <v>47</v>
       </c>
-      <c r="H64" s="83">
+      <c r="H64" s="84">
         <f>IF(G64="ILF",'3. 调整因子'!$D$63,IF(G64="EIF",'3. 调整因子'!$D$64,IF(G64="EI",'3. 调整因子'!$D$65,IF(G64="EO",'3. 调整因子'!$D$66,IF(G64="EQ",'3. 调整因子'!$D$67,"")))))</f>
         <v>5</v>
       </c>
@@ -4886,28 +4888,28 @@
       <c r="L64" s="90"/>
     </row>
     <row r="65" s="57" customFormat="1" spans="1:12">
-      <c r="A65" s="79">
+      <c r="A65" s="75">
         <v>57</v>
       </c>
-      <c r="B65" s="80" t="s">
-        <v>38</v>
-      </c>
-      <c r="C65" s="80" t="s">
-        <v>39</v>
-      </c>
-      <c r="D65" s="80" t="s">
-        <v>40</v>
-      </c>
-      <c r="E65" s="80" t="s">
+      <c r="B65" s="76" t="s">
+        <v>38</v>
+      </c>
+      <c r="C65" s="76" t="s">
+        <v>39</v>
+      </c>
+      <c r="D65" s="76" t="s">
+        <v>40</v>
+      </c>
+      <c r="E65" s="76" t="s">
         <v>40</v>
       </c>
       <c r="F65" s="85" t="s">
         <v>105</v>
       </c>
-      <c r="G65" s="82" t="s">
+      <c r="G65" s="83" t="s">
         <v>47</v>
       </c>
-      <c r="H65" s="83">
+      <c r="H65" s="84">
         <f>IF(G65="ILF",'3. 调整因子'!$D$63,IF(G65="EIF",'3. 调整因子'!$D$64,IF(G65="EI",'3. 调整因子'!$D$65,IF(G65="EO",'3. 调整因子'!$D$66,IF(G65="EQ",'3. 调整因子'!$D$67,"")))))</f>
         <v>5</v>
       </c>
@@ -4924,28 +4926,28 @@
       <c r="L65" s="90"/>
     </row>
     <row r="66" s="57" customFormat="1" spans="1:12">
-      <c r="A66" s="79">
+      <c r="A66" s="75">
         <v>58</v>
       </c>
-      <c r="B66" s="80" t="s">
-        <v>38</v>
-      </c>
-      <c r="C66" s="80" t="s">
-        <v>39</v>
-      </c>
-      <c r="D66" s="80" t="s">
-        <v>40</v>
-      </c>
-      <c r="E66" s="80" t="s">
+      <c r="B66" s="76" t="s">
+        <v>38</v>
+      </c>
+      <c r="C66" s="76" t="s">
+        <v>39</v>
+      </c>
+      <c r="D66" s="76" t="s">
+        <v>40</v>
+      </c>
+      <c r="E66" s="76" t="s">
         <v>40</v>
       </c>
       <c r="F66" s="85" t="s">
         <v>106</v>
       </c>
-      <c r="G66" s="82" t="s">
+      <c r="G66" s="83" t="s">
         <v>47</v>
       </c>
-      <c r="H66" s="83">
+      <c r="H66" s="84">
         <f>IF(G66="ILF",'3. 调整因子'!$D$63,IF(G66="EIF",'3. 调整因子'!$D$64,IF(G66="EI",'3. 调整因子'!$D$65,IF(G66="EO",'3. 调整因子'!$D$66,IF(G66="EQ",'3. 调整因子'!$D$67,"")))))</f>
         <v>5</v>
       </c>
@@ -4961,28 +4963,28 @@
       <c r="L66" s="90"/>
     </row>
     <row r="67" s="57" customFormat="1" spans="1:12">
-      <c r="A67" s="79">
+      <c r="A67" s="75">
         <v>59</v>
       </c>
-      <c r="B67" s="80" t="s">
-        <v>38</v>
-      </c>
-      <c r="C67" s="80" t="s">
-        <v>39</v>
-      </c>
-      <c r="D67" s="80" t="s">
-        <v>40</v>
-      </c>
-      <c r="E67" s="80" t="s">
+      <c r="B67" s="76" t="s">
+        <v>38</v>
+      </c>
+      <c r="C67" s="76" t="s">
+        <v>39</v>
+      </c>
+      <c r="D67" s="76" t="s">
+        <v>40</v>
+      </c>
+      <c r="E67" s="76" t="s">
         <v>40</v>
       </c>
       <c r="F67" s="85" t="s">
         <v>107</v>
       </c>
-      <c r="G67" s="82" t="s">
+      <c r="G67" s="83" t="s">
         <v>47</v>
       </c>
-      <c r="H67" s="83">
+      <c r="H67" s="84">
         <f>IF(G67="ILF",'3. 调整因子'!$D$63,IF(G67="EIF",'3. 调整因子'!$D$64,IF(G67="EI",'3. 调整因子'!$D$65,IF(G67="EO",'3. 调整因子'!$D$66,IF(G67="EQ",'3. 调整因子'!$D$67,"")))))</f>
         <v>5</v>
       </c>
@@ -4999,28 +5001,28 @@
       <c r="L67" s="90"/>
     </row>
     <row r="68" s="57" customFormat="1" spans="1:12">
-      <c r="A68" s="79">
+      <c r="A68" s="75">
         <v>60</v>
       </c>
-      <c r="B68" s="80" t="s">
-        <v>38</v>
-      </c>
-      <c r="C68" s="80" t="s">
-        <v>39</v>
-      </c>
-      <c r="D68" s="80" t="s">
-        <v>40</v>
-      </c>
-      <c r="E68" s="80" t="s">
+      <c r="B68" s="76" t="s">
+        <v>38</v>
+      </c>
+      <c r="C68" s="76" t="s">
+        <v>39</v>
+      </c>
+      <c r="D68" s="76" t="s">
+        <v>40</v>
+      </c>
+      <c r="E68" s="76" t="s">
         <v>40</v>
       </c>
       <c r="F68" s="85" t="s">
         <v>108</v>
       </c>
-      <c r="G68" s="82" t="s">
+      <c r="G68" s="83" t="s">
         <v>47</v>
       </c>
-      <c r="H68" s="83">
+      <c r="H68" s="84">
         <f>IF(G68="ILF",'3. 调整因子'!$D$63,IF(G68="EIF",'3. 调整因子'!$D$64,IF(G68="EI",'3. 调整因子'!$D$65,IF(G68="EO",'3. 调整因子'!$D$66,IF(G68="EQ",'3. 调整因子'!$D$67,"")))))</f>
         <v>5</v>
       </c>
@@ -5037,28 +5039,28 @@
       <c r="L68" s="90"/>
     </row>
     <row r="69" s="57" customFormat="1" spans="1:12">
-      <c r="A69" s="79">
+      <c r="A69" s="75">
         <v>61</v>
       </c>
-      <c r="B69" s="80" t="s">
-        <v>38</v>
-      </c>
-      <c r="C69" s="80" t="s">
-        <v>39</v>
-      </c>
-      <c r="D69" s="80" t="s">
-        <v>40</v>
-      </c>
-      <c r="E69" s="80" t="s">
+      <c r="B69" s="76" t="s">
+        <v>38</v>
+      </c>
+      <c r="C69" s="76" t="s">
+        <v>39</v>
+      </c>
+      <c r="D69" s="76" t="s">
+        <v>40</v>
+      </c>
+      <c r="E69" s="76" t="s">
         <v>40</v>
       </c>
       <c r="F69" s="85" t="s">
         <v>109</v>
       </c>
-      <c r="G69" s="82" t="s">
+      <c r="G69" s="83" t="s">
         <v>47</v>
       </c>
-      <c r="H69" s="83">
+      <c r="H69" s="84">
         <f>IF(G69="ILF",'3. 调整因子'!$D$63,IF(G69="EIF",'3. 调整因子'!$D$64,IF(G69="EI",'3. 调整因子'!$D$65,IF(G69="EO",'3. 调整因子'!$D$66,IF(G69="EQ",'3. 调整因子'!$D$67,"")))))</f>
         <v>5</v>
       </c>
@@ -5075,28 +5077,28 @@
       <c r="L69" s="90"/>
     </row>
     <row r="70" s="58" customFormat="1" spans="1:12">
-      <c r="A70" s="79">
+      <c r="A70" s="75">
         <v>62</v>
       </c>
-      <c r="B70" s="84" t="s">
-        <v>38</v>
-      </c>
-      <c r="C70" s="84" t="s">
-        <v>39</v>
-      </c>
-      <c r="D70" s="84" t="s">
-        <v>40</v>
-      </c>
-      <c r="E70" s="84" t="s">
+      <c r="B70" s="77" t="s">
+        <v>38</v>
+      </c>
+      <c r="C70" s="77" t="s">
+        <v>39</v>
+      </c>
+      <c r="D70" s="77" t="s">
+        <v>40</v>
+      </c>
+      <c r="E70" s="77" t="s">
         <v>40</v>
       </c>
       <c r="F70" s="86" t="s">
         <v>110</v>
       </c>
-      <c r="G70" s="82" t="s">
+      <c r="G70" s="83" t="s">
         <v>51</v>
       </c>
-      <c r="H70" s="83">
+      <c r="H70" s="84">
         <f>IF(G70="ILF",'3. 调整因子'!$D$63,IF(G70="EIF",'3. 调整因子'!$D$64,IF(G70="EI",'3. 调整因子'!$D$65,IF(G70="EO",'3. 调整因子'!$D$66,IF(G70="EQ",'3. 调整因子'!$D$67,"")))))</f>
         <v>7</v>
       </c>
@@ -5112,28 +5114,28 @@
       <c r="L70" s="92"/>
     </row>
     <row r="71" s="55" customFormat="1" spans="1:12">
-      <c r="A71" s="79">
+      <c r="A71" s="75">
         <v>63</v>
       </c>
-      <c r="B71" s="80" t="s">
-        <v>38</v>
-      </c>
-      <c r="C71" s="80" t="s">
-        <v>39</v>
-      </c>
-      <c r="D71" s="80" t="s">
-        <v>40</v>
-      </c>
-      <c r="E71" s="80" t="s">
+      <c r="B71" s="76" t="s">
+        <v>38</v>
+      </c>
+      <c r="C71" s="76" t="s">
+        <v>39</v>
+      </c>
+      <c r="D71" s="76" t="s">
+        <v>40</v>
+      </c>
+      <c r="E71" s="76" t="s">
         <v>40</v>
       </c>
       <c r="F71" s="85" t="s">
         <v>111</v>
       </c>
-      <c r="G71" s="82" t="s">
+      <c r="G71" s="83" t="s">
         <v>54</v>
       </c>
-      <c r="H71" s="83">
+      <c r="H71" s="84">
         <f>IF(G71="ILF",'3. 调整因子'!$D$63,IF(G71="EIF",'3. 调整因子'!$D$64,IF(G71="EI",'3. 调整因子'!$D$65,IF(G71="EO",'3. 调整因子'!$D$66,IF(G71="EQ",'3. 调整因子'!$D$67,"")))))</f>
         <v>4</v>
       </c>
@@ -5150,28 +5152,28 @@
       <c r="L71" s="90"/>
     </row>
     <row r="72" s="55" customFormat="1" spans="1:12">
-      <c r="A72" s="79">
+      <c r="A72" s="75">
         <v>64</v>
       </c>
-      <c r="B72" s="80" t="s">
-        <v>38</v>
-      </c>
-      <c r="C72" s="80" t="s">
-        <v>39</v>
-      </c>
-      <c r="D72" s="80" t="s">
-        <v>40</v>
-      </c>
-      <c r="E72" s="80" t="s">
+      <c r="B72" s="76" t="s">
+        <v>38</v>
+      </c>
+      <c r="C72" s="76" t="s">
+        <v>39</v>
+      </c>
+      <c r="D72" s="76" t="s">
+        <v>40</v>
+      </c>
+      <c r="E72" s="76" t="s">
         <v>40</v>
       </c>
       <c r="F72" s="85" t="s">
         <v>112</v>
       </c>
-      <c r="G72" s="82" t="s">
+      <c r="G72" s="83" t="s">
         <v>47</v>
       </c>
-      <c r="H72" s="83">
+      <c r="H72" s="84">
         <f>IF(G72="ILF",'3. 调整因子'!$D$63,IF(G72="EIF",'3. 调整因子'!$D$64,IF(G72="EI",'3. 调整因子'!$D$65,IF(G72="EO",'3. 调整因子'!$D$66,IF(G72="EQ",'3. 调整因子'!$D$67,"")))))</f>
         <v>5</v>
       </c>
@@ -5188,28 +5190,28 @@
       <c r="L72" s="90"/>
     </row>
     <row r="73" s="57" customFormat="1" spans="1:12">
-      <c r="A73" s="79">
+      <c r="A73" s="75">
         <v>65</v>
       </c>
-      <c r="B73" s="80" t="s">
-        <v>38</v>
-      </c>
-      <c r="C73" s="80" t="s">
-        <v>39</v>
-      </c>
-      <c r="D73" s="80" t="s">
-        <v>40</v>
-      </c>
-      <c r="E73" s="80" t="s">
+      <c r="B73" s="76" t="s">
+        <v>38</v>
+      </c>
+      <c r="C73" s="76" t="s">
+        <v>39</v>
+      </c>
+      <c r="D73" s="76" t="s">
+        <v>40</v>
+      </c>
+      <c r="E73" s="76" t="s">
         <v>40</v>
       </c>
       <c r="F73" s="85" t="s">
         <v>113</v>
       </c>
-      <c r="G73" s="82" t="s">
+      <c r="G73" s="83" t="s">
         <v>47</v>
       </c>
-      <c r="H73" s="83">
+      <c r="H73" s="84">
         <f>IF(G73="ILF",'3. 调整因子'!$D$63,IF(G73="EIF",'3. 调整因子'!$D$64,IF(G73="EI",'3. 调整因子'!$D$65,IF(G73="EO",'3. 调整因子'!$D$66,IF(G73="EQ",'3. 调整因子'!$D$67,"")))))</f>
         <v>5</v>
       </c>
@@ -5226,28 +5228,28 @@
       <c r="L73" s="90"/>
     </row>
     <row r="74" s="57" customFormat="1" spans="1:12">
-      <c r="A74" s="79">
+      <c r="A74" s="75">
         <v>66</v>
       </c>
-      <c r="B74" s="80" t="s">
-        <v>38</v>
-      </c>
-      <c r="C74" s="80" t="s">
-        <v>39</v>
-      </c>
-      <c r="D74" s="80" t="s">
-        <v>40</v>
-      </c>
-      <c r="E74" s="80" t="s">
+      <c r="B74" s="76" t="s">
+        <v>38</v>
+      </c>
+      <c r="C74" s="76" t="s">
+        <v>39</v>
+      </c>
+      <c r="D74" s="76" t="s">
+        <v>40</v>
+      </c>
+      <c r="E74" s="76" t="s">
         <v>40</v>
       </c>
       <c r="F74" s="85" t="s">
         <v>114</v>
       </c>
-      <c r="G74" s="82" t="s">
+      <c r="G74" s="83" t="s">
         <v>47</v>
       </c>
-      <c r="H74" s="83">
+      <c r="H74" s="84">
         <f>IF(G74="ILF",'3. 调整因子'!$D$63,IF(G74="EIF",'3. 调整因子'!$D$64,IF(G74="EI",'3. 调整因子'!$D$65,IF(G74="EO",'3. 调整因子'!$D$66,IF(G74="EQ",'3. 调整因子'!$D$67,"")))))</f>
         <v>5</v>
       </c>
@@ -5264,28 +5266,28 @@
       <c r="L74" s="90"/>
     </row>
     <row r="75" s="57" customFormat="1" spans="1:12">
-      <c r="A75" s="79">
+      <c r="A75" s="75">
         <v>67</v>
       </c>
-      <c r="B75" s="80" t="s">
-        <v>38</v>
-      </c>
-      <c r="C75" s="80" t="s">
-        <v>39</v>
-      </c>
-      <c r="D75" s="80" t="s">
-        <v>40</v>
-      </c>
-      <c r="E75" s="80" t="s">
+      <c r="B75" s="76" t="s">
+        <v>38</v>
+      </c>
+      <c r="C75" s="76" t="s">
+        <v>39</v>
+      </c>
+      <c r="D75" s="76" t="s">
+        <v>40</v>
+      </c>
+      <c r="E75" s="76" t="s">
         <v>40</v>
       </c>
       <c r="F75" s="85" t="s">
         <v>115</v>
       </c>
-      <c r="G75" s="82" t="s">
+      <c r="G75" s="83" t="s">
         <v>47</v>
       </c>
-      <c r="H75" s="83">
+      <c r="H75" s="84">
         <f>IF(G75="ILF",'3. 调整因子'!$D$63,IF(G75="EIF",'3. 调整因子'!$D$64,IF(G75="EI",'3. 调整因子'!$D$65,IF(G75="EO",'3. 调整因子'!$D$66,IF(G75="EQ",'3. 调整因子'!$D$67,"")))))</f>
         <v>5</v>
       </c>
@@ -5302,28 +5304,28 @@
       <c r="L75" s="90"/>
     </row>
     <row r="76" s="57" customFormat="1" spans="1:12">
-      <c r="A76" s="79">
+      <c r="A76" s="75">
         <v>68</v>
       </c>
-      <c r="B76" s="80" t="s">
-        <v>38</v>
-      </c>
-      <c r="C76" s="80" t="s">
-        <v>39</v>
-      </c>
-      <c r="D76" s="80" t="s">
-        <v>40</v>
-      </c>
-      <c r="E76" s="80" t="s">
+      <c r="B76" s="76" t="s">
+        <v>38</v>
+      </c>
+      <c r="C76" s="76" t="s">
+        <v>39</v>
+      </c>
+      <c r="D76" s="76" t="s">
+        <v>40</v>
+      </c>
+      <c r="E76" s="76" t="s">
         <v>40</v>
       </c>
       <c r="F76" s="85" t="s">
         <v>116</v>
       </c>
-      <c r="G76" s="82" t="s">
+      <c r="G76" s="83" t="s">
         <v>47</v>
       </c>
-      <c r="H76" s="83">
+      <c r="H76" s="84">
         <f>IF(G76="ILF",'3. 调整因子'!$D$63,IF(G76="EIF",'3. 调整因子'!$D$64,IF(G76="EI",'3. 调整因子'!$D$65,IF(G76="EO",'3. 调整因子'!$D$66,IF(G76="EQ",'3. 调整因子'!$D$67,"")))))</f>
         <v>5</v>
       </c>
@@ -5339,28 +5341,28 @@
       <c r="L76" s="90"/>
     </row>
     <row r="77" s="57" customFormat="1" spans="1:12">
-      <c r="A77" s="79">
+      <c r="A77" s="75">
         <v>69</v>
       </c>
-      <c r="B77" s="80" t="s">
-        <v>38</v>
-      </c>
-      <c r="C77" s="80" t="s">
-        <v>39</v>
-      </c>
-      <c r="D77" s="80" t="s">
-        <v>40</v>
-      </c>
-      <c r="E77" s="80" t="s">
+      <c r="B77" s="76" t="s">
+        <v>38</v>
+      </c>
+      <c r="C77" s="76" t="s">
+        <v>39</v>
+      </c>
+      <c r="D77" s="76" t="s">
+        <v>40</v>
+      </c>
+      <c r="E77" s="76" t="s">
         <v>40</v>
       </c>
       <c r="F77" s="85" t="s">
         <v>117</v>
       </c>
-      <c r="G77" s="82" t="s">
+      <c r="G77" s="83" t="s">
         <v>47</v>
       </c>
-      <c r="H77" s="83">
+      <c r="H77" s="84">
         <f>IF(G77="ILF",'3. 调整因子'!$D$63,IF(G77="EIF",'3. 调整因子'!$D$64,IF(G77="EI",'3. 调整因子'!$D$65,IF(G77="EO",'3. 调整因子'!$D$66,IF(G77="EQ",'3. 调整因子'!$D$67,"")))))</f>
         <v>5</v>
       </c>
@@ -5377,28 +5379,28 @@
       <c r="L77" s="90"/>
     </row>
     <row r="78" s="57" customFormat="1" spans="1:12">
-      <c r="A78" s="79">
+      <c r="A78" s="75">
         <v>70</v>
       </c>
-      <c r="B78" s="80" t="s">
-        <v>38</v>
-      </c>
-      <c r="C78" s="80" t="s">
-        <v>39</v>
-      </c>
-      <c r="D78" s="80" t="s">
-        <v>40</v>
-      </c>
-      <c r="E78" s="80" t="s">
+      <c r="B78" s="76" t="s">
+        <v>38</v>
+      </c>
+      <c r="C78" s="76" t="s">
+        <v>39</v>
+      </c>
+      <c r="D78" s="76" t="s">
+        <v>40</v>
+      </c>
+      <c r="E78" s="76" t="s">
         <v>40</v>
       </c>
       <c r="F78" s="85" t="s">
         <v>118</v>
       </c>
-      <c r="G78" s="82" t="s">
+      <c r="G78" s="83" t="s">
         <v>47</v>
       </c>
-      <c r="H78" s="83">
+      <c r="H78" s="84">
         <f>IF(G78="ILF",'3. 调整因子'!$D$63,IF(G78="EIF",'3. 调整因子'!$D$64,IF(G78="EI",'3. 调整因子'!$D$65,IF(G78="EO",'3. 调整因子'!$D$66,IF(G78="EQ",'3. 调整因子'!$D$67,"")))))</f>
         <v>5</v>
       </c>
@@ -5415,28 +5417,28 @@
       <c r="L78" s="90"/>
     </row>
     <row r="79" s="57" customFormat="1" spans="1:12">
-      <c r="A79" s="79">
+      <c r="A79" s="75">
         <v>71</v>
       </c>
-      <c r="B79" s="80" t="s">
-        <v>38</v>
-      </c>
-      <c r="C79" s="80" t="s">
-        <v>39</v>
-      </c>
-      <c r="D79" s="80" t="s">
-        <v>40</v>
-      </c>
-      <c r="E79" s="80" t="s">
+      <c r="B79" s="76" t="s">
+        <v>38</v>
+      </c>
+      <c r="C79" s="76" t="s">
+        <v>39</v>
+      </c>
+      <c r="D79" s="76" t="s">
+        <v>40</v>
+      </c>
+      <c r="E79" s="76" t="s">
         <v>40</v>
       </c>
       <c r="F79" s="85" t="s">
         <v>119</v>
       </c>
-      <c r="G79" s="82" t="s">
+      <c r="G79" s="83" t="s">
         <v>47</v>
       </c>
-      <c r="H79" s="83">
+      <c r="H79" s="84">
         <f>IF(G79="ILF",'3. 调整因子'!$D$63,IF(G79="EIF",'3. 调整因子'!$D$64,IF(G79="EI",'3. 调整因子'!$D$65,IF(G79="EO",'3. 调整因子'!$D$66,IF(G79="EQ",'3. 调整因子'!$D$67,"")))))</f>
         <v>5</v>
       </c>
@@ -5453,28 +5455,28 @@
       <c r="L79" s="90"/>
     </row>
     <row r="80" s="57" customFormat="1" spans="1:12">
-      <c r="A80" s="79">
+      <c r="A80" s="75">
         <v>72</v>
       </c>
-      <c r="B80" s="80" t="s">
-        <v>38</v>
-      </c>
-      <c r="C80" s="80" t="s">
-        <v>39</v>
-      </c>
-      <c r="D80" s="80" t="s">
-        <v>40</v>
-      </c>
-      <c r="E80" s="80" t="s">
+      <c r="B80" s="76" t="s">
+        <v>38</v>
+      </c>
+      <c r="C80" s="76" t="s">
+        <v>39</v>
+      </c>
+      <c r="D80" s="76" t="s">
+        <v>40</v>
+      </c>
+      <c r="E80" s="76" t="s">
         <v>40</v>
       </c>
       <c r="F80" s="85" t="s">
         <v>120</v>
       </c>
-      <c r="G80" s="82" t="s">
+      <c r="G80" s="83" t="s">
         <v>42</v>
       </c>
-      <c r="H80" s="83">
+      <c r="H80" s="84">
         <f>IF(G80="ILF",'3. 调整因子'!$D$63,IF(G80="EIF",'3. 调整因子'!$D$64,IF(G80="EI",'3. 调整因子'!$D$65,IF(G80="EO",'3. 调整因子'!$D$66,IF(G80="EQ",'3. 调整因子'!$D$67,"")))))</f>
         <v>4</v>
       </c>
@@ -5490,28 +5492,28 @@
       <c r="L80" s="90"/>
     </row>
     <row r="81" s="57" customFormat="1" spans="1:12">
-      <c r="A81" s="79">
+      <c r="A81" s="75">
         <v>73</v>
       </c>
-      <c r="B81" s="80" t="s">
-        <v>38</v>
-      </c>
-      <c r="C81" s="80" t="s">
-        <v>39</v>
-      </c>
-      <c r="D81" s="80" t="s">
-        <v>40</v>
-      </c>
-      <c r="E81" s="80" t="s">
+      <c r="B81" s="76" t="s">
+        <v>38</v>
+      </c>
+      <c r="C81" s="76" t="s">
+        <v>39</v>
+      </c>
+      <c r="D81" s="76" t="s">
+        <v>40</v>
+      </c>
+      <c r="E81" s="76" t="s">
         <v>40</v>
       </c>
       <c r="F81" s="85" t="s">
         <v>121</v>
       </c>
-      <c r="G81" s="82" t="s">
+      <c r="G81" s="83" t="s">
         <v>47</v>
       </c>
-      <c r="H81" s="83">
+      <c r="H81" s="84">
         <f>IF(G81="ILF",'3. 调整因子'!$D$63,IF(G81="EIF",'3. 调整因子'!$D$64,IF(G81="EI",'3. 调整因子'!$D$65,IF(G81="EO",'3. 调整因子'!$D$66,IF(G81="EQ",'3. 调整因子'!$D$67,"")))))</f>
         <v>5</v>
       </c>
@@ -5528,28 +5530,28 @@
       <c r="L81" s="90"/>
     </row>
     <row r="82" s="58" customFormat="1" spans="1:12">
-      <c r="A82" s="79">
+      <c r="A82" s="75">
         <v>74</v>
       </c>
-      <c r="B82" s="84" t="s">
-        <v>38</v>
-      </c>
-      <c r="C82" s="84" t="s">
-        <v>39</v>
-      </c>
-      <c r="D82" s="84" t="s">
-        <v>40</v>
-      </c>
-      <c r="E82" s="84" t="s">
+      <c r="B82" s="77" t="s">
+        <v>38</v>
+      </c>
+      <c r="C82" s="77" t="s">
+        <v>39</v>
+      </c>
+      <c r="D82" s="77" t="s">
+        <v>40</v>
+      </c>
+      <c r="E82" s="77" t="s">
         <v>40</v>
       </c>
       <c r="F82" s="86" t="s">
         <v>122</v>
       </c>
-      <c r="G82" s="82" t="s">
+      <c r="G82" s="83" t="s">
         <v>51</v>
       </c>
-      <c r="H82" s="83">
+      <c r="H82" s="84">
         <f>IF(G82="ILF",'3. 调整因子'!$D$63,IF(G82="EIF",'3. 调整因子'!$D$64,IF(G82="EI",'3. 调整因子'!$D$65,IF(G82="EO",'3. 调整因子'!$D$66,IF(G82="EQ",'3. 调整因子'!$D$67,"")))))</f>
         <v>7</v>
       </c>
@@ -5566,28 +5568,28 @@
       <c r="L82" s="92"/>
     </row>
     <row r="83" s="58" customFormat="1" spans="1:12">
-      <c r="A83" s="79">
+      <c r="A83" s="75">
         <v>75</v>
       </c>
-      <c r="B83" s="84" t="s">
-        <v>38</v>
-      </c>
-      <c r="C83" s="84" t="s">
-        <v>39</v>
-      </c>
-      <c r="D83" s="84" t="s">
-        <v>40</v>
-      </c>
-      <c r="E83" s="84" t="s">
-        <v>40</v>
-      </c>
-      <c r="F83" s="84" t="s">
+      <c r="B83" s="77" t="s">
+        <v>38</v>
+      </c>
+      <c r="C83" s="77" t="s">
+        <v>39</v>
+      </c>
+      <c r="D83" s="77" t="s">
+        <v>40</v>
+      </c>
+      <c r="E83" s="77" t="s">
+        <v>40</v>
+      </c>
+      <c r="F83" s="77" t="s">
         <v>123</v>
       </c>
-      <c r="G83" s="82" t="s">
+      <c r="G83" s="83" t="s">
         <v>51</v>
       </c>
-      <c r="H83" s="83">
+      <c r="H83" s="84">
         <f>IF(G83="ILF",'3. 调整因子'!$D$63,IF(G83="EIF",'3. 调整因子'!$D$64,IF(G83="EI",'3. 调整因子'!$D$65,IF(G83="EO",'3. 调整因子'!$D$66,IF(G83="EQ",'3. 调整因子'!$D$67,"")))))</f>
         <v>7</v>
       </c>
@@ -5604,7 +5606,7 @@
       <c r="L83" s="92"/>
     </row>
     <row r="84" s="59" customFormat="1" spans="1:12">
-      <c r="A84" s="79"/>
+      <c r="A84" s="75"/>
       <c r="B84" s="93" t="s">
         <v>124</v>
       </c>
@@ -5621,13 +5623,13 @@
       <c r="J84" s="97"/>
       <c r="K84" s="96">
         <f>SUM(K9:K83)</f>
-        <v>122.6</v>
+        <v>125.266666666666</v>
       </c>
       <c r="L84" s="98"/>
     </row>
   </sheetData>
   <sheetProtection formatCells="0" formatColumns="0" formatRows="0" insertRows="0" insertHyperlinks="0" deleteRows="0" sort="0"/>
-  <autoFilter ref="A7:L84" etc:filterBottomFollowUsedRange="0">
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A7:L84" etc:filterBottomFollowUsedRange="0">
     <extLst/>
   </autoFilter>
   <mergeCells count="10">
@@ -5719,140 +5721,140 @@
     <tabColor rgb="FFFFFF00"/>
   </sheetPr>
   <dimension ref="A1:I97"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.75"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15.2"/>
   <cols>
-    <col min="1" max="1" customWidth="true" style="24" width="5.17699115044248" collapsed="false"/>
-    <col min="2" max="2" customWidth="true" style="24" width="11.8141592920354" collapsed="false"/>
-    <col min="3" max="3" customWidth="true" style="25" width="84.4513274336283" collapsed="false"/>
-    <col min="4" max="4" customWidth="true" style="23" width="11.4513274336283" collapsed="false"/>
-    <col min="5" max="5" customWidth="true" style="26" width="32.5575221238938" collapsed="false"/>
-    <col min="6" max="6" customWidth="true" style="25" width="6.45132743362832" collapsed="false"/>
-    <col min="7" max="7" customWidth="true" style="25" width="10.6283185840708" collapsed="false"/>
-    <col min="8" max="16384" style="25" width="9.0" collapsed="false"/>
+    <col min="1" max="1" width="5.17307692307692" style="24" customWidth="1"/>
+    <col min="2" max="2" width="11.8173076923077" style="24" customWidth="1"/>
+    <col min="3" max="3" width="84.4519230769231" style="25" customWidth="1"/>
+    <col min="4" max="4" width="11.4519230769231" style="23" customWidth="1"/>
+    <col min="5" max="5" width="32.5576923076923" style="26" customWidth="1"/>
+    <col min="6" max="6" width="6.45192307692308" style="25" customWidth="1"/>
+    <col min="7" max="7" width="10.625" style="25" customWidth="1"/>
+    <col min="8" max="16384" width="9" style="25"/>
   </cols>
   <sheetData>
-    <row r="1" s="3" customFormat="1" ht="40" customHeight="1" spans="1:9">
+    <row r="1" s="20" customFormat="1" ht="40" customHeight="1" spans="1:9">
       <c r="A1" s="27" t="s">
         <v>125</v>
       </c>
       <c r="B1" s="27"/>
       <c r="C1" s="27"/>
       <c r="D1" s="27"/>
-      <c r="E1" s="28"/>
-      <c r="F1" s="28"/>
-      <c r="G1" s="28"/>
-      <c r="H1" s="28"/>
-      <c r="I1" s="28"/>
+      <c r="E1" s="49"/>
+      <c r="F1" s="49"/>
+      <c r="G1" s="49"/>
+      <c r="H1" s="49"/>
+      <c r="I1" s="49"/>
     </row>
     <row r="2" spans="1:5">
-      <c r="A2" s="29" t="s">
+      <c r="A2" s="28" t="s">
         <v>126</v>
       </c>
-      <c r="B2" s="29"/>
-      <c r="C2" s="30" t="s">
+      <c r="B2" s="28"/>
+      <c r="C2" s="29" t="s">
         <v>127</v>
       </c>
-      <c r="D2" s="31">
+      <c r="D2" s="30">
         <f>IF('3. 调整因子'!C2='3. 调整因子'!B36,'3. 调整因子'!D36,IF('3. 调整因子'!C2='3. 调整因子'!B37,'3. 调整因子'!D37,IF('3. 调整因子'!C2='3. 调整因子'!B38,'3. 调整因子'!D38,IF('3. 调整因子'!C2='3. 调整因子'!B39,'3. 调整因子'!D39,0))))</f>
         <v>1.21</v>
       </c>
       <c r="E2" s="25"/>
     </row>
     <row r="3" spans="1:5">
-      <c r="A3" s="29" t="s">
+      <c r="A3" s="28" t="s">
         <v>128</v>
       </c>
-      <c r="B3" s="29"/>
-      <c r="C3" s="30" t="s">
+      <c r="B3" s="28"/>
+      <c r="C3" s="29" t="s">
         <v>129</v>
       </c>
-      <c r="D3" s="32">
+      <c r="D3" s="31">
         <f>IF(C3=B12,D12,IF(C3=B13,D13,IF(C3=B14,D14,IF(C3=B15,D15,IF(C3=B16,D16,IF(C3=B17,D17,IF(C3=B18,D18,IF(C3=B19,D19,0))))))))</f>
         <v>1</v>
       </c>
       <c r="E3" s="25"/>
     </row>
-    <row r="4" spans="1:5">
-      <c r="A4" s="29" t="s">
+    <row r="4" ht="16" spans="1:5">
+      <c r="A4" s="28" t="s">
         <v>130</v>
       </c>
-      <c r="B4" s="33" t="s">
+      <c r="B4" s="32" t="s">
         <v>131</v>
       </c>
-      <c r="C4" s="34" t="s">
+      <c r="C4" s="33" t="s">
         <v>132</v>
       </c>
-      <c r="D4" s="35">
+      <c r="D4" s="34">
         <f>IF(C4=C22,D22,IF(C4=C23,D23,IF(C4=C24,D24,-10)))</f>
         <v>-1</v>
       </c>
-      <c r="E4" s="36"/>
-    </row>
-    <row r="5" spans="1:5">
-      <c r="A5" s="29"/>
-      <c r="B5" s="33" t="s">
+      <c r="E4" s="50"/>
+    </row>
+    <row r="5" ht="16" spans="1:5">
+      <c r="A5" s="28"/>
+      <c r="B5" s="32" t="s">
         <v>133</v>
       </c>
-      <c r="C5" s="34" t="s">
+      <c r="C5" s="33" t="s">
         <v>134</v>
       </c>
-      <c r="D5" s="35">
+      <c r="D5" s="34">
         <f>IF(C5=C25,D25,IF(C5=C26,D26,IF(C5=C27,D27,-10)))</f>
         <v>-1</v>
       </c>
-      <c r="E5" s="36"/>
-    </row>
-    <row r="6" spans="1:5">
-      <c r="A6" s="29"/>
-      <c r="B6" s="33" t="s">
+      <c r="E5" s="50"/>
+    </row>
+    <row r="6" ht="16" spans="1:5">
+      <c r="A6" s="28"/>
+      <c r="B6" s="32" t="s">
         <v>135</v>
       </c>
-      <c r="C6" s="34" t="s">
+      <c r="C6" s="33" t="s">
         <v>136</v>
       </c>
-      <c r="D6" s="35">
+      <c r="D6" s="34">
         <f>IF(C6=C28,D28,IF(C6=C29,D29,IF(C6=C30,D30,-10)))</f>
         <v>-1</v>
       </c>
-      <c r="E6" s="36"/>
-    </row>
-    <row r="7" spans="1:5">
-      <c r="A7" s="29"/>
-      <c r="B7" s="33" t="s">
+      <c r="E6" s="50"/>
+    </row>
+    <row r="7" ht="16" spans="1:5">
+      <c r="A7" s="28"/>
+      <c r="B7" s="32" t="s">
         <v>137</v>
       </c>
-      <c r="C7" s="34" t="s">
+      <c r="C7" s="33" t="s">
         <v>138</v>
       </c>
-      <c r="D7" s="35">
+      <c r="D7" s="34">
         <f>IF(C7=C31,D31,IF(C7=C32,D32,IF(C7=C33,D33,-10)))</f>
         <v>-1</v>
       </c>
-      <c r="E7" s="36"/>
+      <c r="E7" s="50"/>
     </row>
     <row r="8" spans="1:5">
-      <c r="A8" s="29" t="s">
+      <c r="A8" s="28" t="s">
         <v>139</v>
       </c>
-      <c r="B8" s="29"/>
-      <c r="C8" s="37" t="s">
+      <c r="B8" s="28"/>
+      <c r="C8" s="35" t="s">
         <v>140</v>
       </c>
-      <c r="D8" s="32">
+      <c r="D8" s="31">
         <f>IF(C8=B43,D43,IF(C8=B44,D44,IF(C8=B45,D45,0)))</f>
         <v>1</v>
       </c>
       <c r="E8" s="25"/>
     </row>
-    <row r="9" spans="1:5">
-      <c r="A9" s="29" t="s">
+    <row r="9" ht="16" spans="1:5">
+      <c r="A9" s="28" t="s">
         <v>141</v>
       </c>
-      <c r="B9" s="29"/>
-      <c r="C9" s="34" t="s">
+      <c r="B9" s="28"/>
+      <c r="C9" s="33" t="s">
         <v>142</v>
       </c>
-      <c r="D9" s="32">
+      <c r="D9" s="31">
         <f>IF(C9=B48,D48,IF(C9=B49,D49,IF(C9=B50,D50,0)))</f>
         <v>0.8</v>
       </c>
@@ -5861,110 +5863,110 @@
     <row r="10" spans="5:5">
       <c r="E10" s="25"/>
     </row>
-    <row r="11" spans="2:5">
-      <c r="B11" s="38" t="s">
+    <row r="11" ht="16" spans="2:5">
+      <c r="B11" s="36" t="s">
         <v>128</v>
       </c>
-      <c r="C11" s="38" t="s">
+      <c r="C11" s="36" t="s">
         <v>143</v>
       </c>
-      <c r="D11" s="38" t="s">
+      <c r="D11" s="36" t="s">
         <v>144</v>
       </c>
       <c r="E11" s="25"/>
     </row>
-    <row r="12" spans="2:5">
-      <c r="B12" s="39" t="s">
+    <row r="12" ht="16" spans="2:5">
+      <c r="B12" s="37" t="s">
         <v>129</v>
       </c>
-      <c r="C12" s="40" t="s">
+      <c r="C12" s="38" t="s">
         <v>145</v>
       </c>
-      <c r="D12" s="41">
+      <c r="D12" s="39">
         <v>1</v>
       </c>
       <c r="E12" s="25"/>
     </row>
-    <row r="13" spans="2:5">
-      <c r="B13" s="39" t="s">
+    <row r="13" ht="16" spans="2:5">
+      <c r="B13" s="37" t="s">
         <v>146</v>
       </c>
-      <c r="C13" s="40" t="s">
+      <c r="C13" s="38" t="s">
         <v>147</v>
       </c>
-      <c r="D13" s="41">
+      <c r="D13" s="39">
         <v>1.2</v>
       </c>
       <c r="E13" s="25"/>
     </row>
-    <row r="14" spans="2:5">
-      <c r="B14" s="39" t="s">
+    <row r="14" ht="16" spans="2:5">
+      <c r="B14" s="37" t="s">
         <v>148</v>
       </c>
-      <c r="C14" s="40" t="s">
+      <c r="C14" s="38" t="s">
         <v>149</v>
       </c>
-      <c r="D14" s="41">
+      <c r="D14" s="39">
         <v>1.2</v>
       </c>
       <c r="E14" s="25"/>
     </row>
-    <row r="15" spans="2:5">
-      <c r="B15" s="39" t="s">
+    <row r="15" ht="16" spans="2:5">
+      <c r="B15" s="37" t="s">
         <v>150</v>
       </c>
-      <c r="C15" s="40" t="s">
+      <c r="C15" s="38" t="s">
         <v>151</v>
       </c>
-      <c r="D15" s="41">
+      <c r="D15" s="39">
         <v>1.5</v>
       </c>
       <c r="E15" s="25"/>
     </row>
-    <row r="16" spans="2:5">
-      <c r="B16" s="39" t="s">
+    <row r="16" ht="16" spans="2:5">
+      <c r="B16" s="37" t="s">
         <v>152</v>
       </c>
-      <c r="C16" s="40" t="s">
+      <c r="C16" s="38" t="s">
         <v>153</v>
       </c>
-      <c r="D16" s="41">
+      <c r="D16" s="39">
         <v>1.7</v>
       </c>
       <c r="E16" s="25"/>
     </row>
-    <row r="17" ht="25.5" spans="2:5">
-      <c r="B17" s="39" t="s">
+    <row r="17" ht="31" spans="2:5">
+      <c r="B17" s="37" t="s">
         <v>154</v>
       </c>
-      <c r="C17" s="40" t="s">
+      <c r="C17" s="38" t="s">
         <v>155</v>
       </c>
-      <c r="D17" s="41">
+      <c r="D17" s="39">
         <v>1.7</v>
       </c>
       <c r="E17" s="25"/>
     </row>
-    <row r="18" spans="2:5">
-      <c r="B18" s="39" t="s">
+    <row r="18" ht="16" spans="2:5">
+      <c r="B18" s="37" t="s">
         <v>156</v>
       </c>
-      <c r="C18" s="40" t="s">
+      <c r="C18" s="38" t="s">
         <v>157</v>
       </c>
-      <c r="D18" s="41">
+      <c r="D18" s="39">
         <v>1.9</v>
       </c>
       <c r="E18" s="25"/>
     </row>
-    <row r="19" spans="2:5">
-      <c r="B19" s="39" t="s">
+    <row r="19" ht="16" spans="2:5">
+      <c r="B19" s="37" t="s">
         <v>158</v>
       </c>
-      <c r="C19" s="40" t="s">
+      <c r="C19" s="38" t="s">
         <v>159</v>
       </c>
-      <c r="D19" s="41">
+      <c r="D19" s="39">
         <v>2</v>
       </c>
       <c r="E19" s="25"/>
@@ -5972,142 +5974,142 @@
     <row r="20" spans="5:5">
       <c r="E20" s="25"/>
     </row>
-    <row r="21" spans="2:5">
-      <c r="B21" s="38" t="s">
+    <row r="21" ht="16" spans="2:5">
+      <c r="B21" s="36" t="s">
         <v>144</v>
       </c>
-      <c r="C21" s="38" t="s">
+      <c r="C21" s="36" t="s">
         <v>160</v>
       </c>
-      <c r="D21" s="38" t="s">
+      <c r="D21" s="36" t="s">
         <v>144</v>
       </c>
       <c r="E21" s="25"/>
     </row>
-    <row r="22" spans="2:5">
-      <c r="B22" s="39" t="s">
+    <row r="22" ht="16" spans="2:5">
+      <c r="B22" s="37" t="s">
         <v>131</v>
       </c>
-      <c r="C22" s="40" t="s">
+      <c r="C22" s="38" t="s">
         <v>132</v>
       </c>
-      <c r="D22" s="39">
+      <c r="D22" s="37">
         <v>-1</v>
       </c>
       <c r="E22" s="25"/>
     </row>
-    <row r="23" spans="2:5">
-      <c r="B23" s="39"/>
-      <c r="C23" s="40" t="s">
+    <row r="23" ht="16" spans="2:5">
+      <c r="B23" s="37"/>
+      <c r="C23" s="38" t="s">
         <v>161</v>
       </c>
-      <c r="D23" s="39">
+      <c r="D23" s="37">
         <v>0</v>
       </c>
       <c r="E23" s="25"/>
     </row>
-    <row r="24" spans="2:5">
-      <c r="B24" s="39"/>
-      <c r="C24" s="40" t="s">
+    <row r="24" ht="16" spans="2:5">
+      <c r="B24" s="37"/>
+      <c r="C24" s="38" t="s">
         <v>162</v>
       </c>
-      <c r="D24" s="39">
+      <c r="D24" s="37">
         <v>1</v>
       </c>
       <c r="E24" s="25"/>
     </row>
-    <row r="25" spans="2:5">
-      <c r="B25" s="39" t="s">
+    <row r="25" ht="16" spans="2:5">
+      <c r="B25" s="37" t="s">
         <v>133</v>
       </c>
-      <c r="C25" s="40" t="s">
+      <c r="C25" s="38" t="s">
         <v>134</v>
       </c>
-      <c r="D25" s="39">
+      <c r="D25" s="37">
         <v>-1</v>
       </c>
       <c r="E25" s="25"/>
     </row>
-    <row r="26" spans="2:5">
-      <c r="B26" s="39"/>
-      <c r="C26" s="40" t="s">
+    <row r="26" ht="16" spans="2:5">
+      <c r="B26" s="37"/>
+      <c r="C26" s="38" t="s">
         <v>163</v>
       </c>
-      <c r="D26" s="39">
+      <c r="D26" s="37">
         <v>0</v>
       </c>
       <c r="E26" s="25"/>
     </row>
-    <row r="27" spans="2:5">
-      <c r="B27" s="39"/>
-      <c r="C27" s="40" t="s">
+    <row r="27" ht="16" spans="2:5">
+      <c r="B27" s="37"/>
+      <c r="C27" s="38" t="s">
         <v>164</v>
       </c>
-      <c r="D27" s="39">
+      <c r="D27" s="37">
         <v>1</v>
       </c>
       <c r="E27" s="25"/>
     </row>
-    <row r="28" spans="2:5">
-      <c r="B28" s="39" t="s">
+    <row r="28" ht="16" spans="2:5">
+      <c r="B28" s="37" t="s">
         <v>135</v>
       </c>
-      <c r="C28" s="40" t="s">
+      <c r="C28" s="38" t="s">
         <v>136</v>
       </c>
-      <c r="D28" s="39">
+      <c r="D28" s="37">
         <v>-1</v>
       </c>
       <c r="E28" s="25"/>
     </row>
-    <row r="29" spans="2:5">
-      <c r="B29" s="39"/>
-      <c r="C29" s="40" t="s">
+    <row r="29" ht="16" spans="2:5">
+      <c r="B29" s="37"/>
+      <c r="C29" s="38" t="s">
         <v>165</v>
       </c>
-      <c r="D29" s="39">
+      <c r="D29" s="37">
         <v>0</v>
       </c>
       <c r="E29" s="25"/>
     </row>
-    <row r="30" spans="2:5">
-      <c r="B30" s="39"/>
-      <c r="C30" s="40" t="s">
+    <row r="30" ht="16" spans="2:5">
+      <c r="B30" s="37"/>
+      <c r="C30" s="38" t="s">
         <v>166</v>
       </c>
-      <c r="D30" s="39">
+      <c r="D30" s="37">
         <v>1</v>
       </c>
       <c r="E30" s="25"/>
     </row>
-    <row r="31" spans="2:5">
-      <c r="B31" s="39" t="s">
+    <row r="31" ht="16" spans="2:5">
+      <c r="B31" s="37" t="s">
         <v>137</v>
       </c>
-      <c r="C31" s="40" t="s">
+      <c r="C31" s="38" t="s">
         <v>138</v>
       </c>
-      <c r="D31" s="39">
+      <c r="D31" s="37">
         <v>-1</v>
       </c>
       <c r="E31" s="25"/>
     </row>
-    <row r="32" spans="2:5">
-      <c r="B32" s="39"/>
-      <c r="C32" s="40" t="s">
+    <row r="32" ht="16" spans="2:5">
+      <c r="B32" s="37"/>
+      <c r="C32" s="38" t="s">
         <v>167</v>
       </c>
-      <c r="D32" s="39">
+      <c r="D32" s="37">
         <v>0</v>
       </c>
       <c r="E32" s="25"/>
     </row>
-    <row r="33" spans="2:5">
-      <c r="B33" s="39"/>
-      <c r="C33" s="40" t="s">
+    <row r="33" ht="16" spans="2:5">
+      <c r="B33" s="37"/>
+      <c r="C33" s="38" t="s">
         <v>168</v>
       </c>
-      <c r="D33" s="39">
+      <c r="D33" s="37">
         <v>1</v>
       </c>
       <c r="E33" s="25"/>
@@ -6116,106 +6118,106 @@
       <c r="E34" s="25"/>
     </row>
     <row r="35" spans="2:5">
-      <c r="B35" s="42" t="s">
+      <c r="B35" s="40" t="s">
         <v>169</v>
       </c>
-      <c r="C35" s="42"/>
-      <c r="D35" s="42"/>
+      <c r="C35" s="40"/>
+      <c r="D35" s="40"/>
       <c r="E35" s="25"/>
     </row>
     <row r="36" spans="2:5">
-      <c r="B36" s="43" t="s">
+      <c r="B36" s="41" t="s">
         <v>170</v>
       </c>
-      <c r="C36" s="44" t="s">
+      <c r="C36" s="42" t="s">
         <v>171</v>
       </c>
-      <c r="D36" s="45">
+      <c r="D36" s="43">
         <v>1.39</v>
       </c>
       <c r="E36" s="25"/>
     </row>
     <row r="37" spans="2:5">
-      <c r="B37" s="43" t="s">
+      <c r="B37" s="41" t="s">
         <v>127</v>
       </c>
-      <c r="C37" s="44" t="s">
+      <c r="C37" s="42" t="s">
         <v>172</v>
       </c>
-      <c r="D37" s="45">
+      <c r="D37" s="43">
         <v>1.21</v>
       </c>
       <c r="E37" s="25"/>
     </row>
     <row r="38" spans="2:5">
-      <c r="B38" s="43" t="s">
+      <c r="B38" s="41" t="s">
         <v>173</v>
       </c>
-      <c r="C38" s="44" t="s">
+      <c r="C38" s="42" t="s">
         <v>174</v>
       </c>
-      <c r="D38" s="45">
+      <c r="D38" s="43">
         <v>1.1</v>
       </c>
       <c r="E38" s="25"/>
     </row>
     <row r="39" spans="2:5">
-      <c r="B39" s="43" t="s">
+      <c r="B39" s="41" t="s">
         <v>175</v>
       </c>
-      <c r="C39" s="44" t="s">
+      <c r="C39" s="42" t="s">
         <v>176</v>
       </c>
-      <c r="D39" s="45">
+      <c r="D39" s="43">
         <v>1</v>
       </c>
       <c r="E39" s="25"/>
     </row>
     <row r="40" spans="2:5">
-      <c r="B40" s="46"/>
-      <c r="C40" s="46"/>
-      <c r="D40" s="47"/>
+      <c r="B40" s="44"/>
+      <c r="C40" s="44"/>
+      <c r="D40" s="45"/>
       <c r="E40" s="25"/>
     </row>
     <row r="41" spans="5:5">
       <c r="E41" s="25"/>
     </row>
-    <row r="42" spans="2:5">
-      <c r="B42" s="29" t="s">
+    <row r="42" ht="16" spans="2:5">
+      <c r="B42" s="28" t="s">
         <v>139</v>
       </c>
-      <c r="C42" s="29"/>
-      <c r="D42" s="29" t="s">
+      <c r="C42" s="28"/>
+      <c r="D42" s="28" t="s">
         <v>144</v>
       </c>
       <c r="E42" s="25"/>
     </row>
     <row r="43" spans="2:5">
-      <c r="B43" s="39" t="s">
+      <c r="B43" s="37" t="s">
         <v>177</v>
       </c>
-      <c r="C43" s="39"/>
-      <c r="D43" s="41">
+      <c r="C43" s="37"/>
+      <c r="D43" s="39">
         <v>1.2</v>
       </c>
       <c r="E43" s="25"/>
     </row>
     <row r="44" spans="2:5">
-      <c r="B44" s="39" t="s">
+      <c r="B44" s="37" t="s">
         <v>140</v>
       </c>
-      <c r="C44" s="39"/>
-      <c r="D44" s="41">
+      <c r="C44" s="37"/>
+      <c r="D44" s="39">
         <v>1</v>
       </c>
       <c r="E44" s="25"/>
     </row>
     <row r="45" spans="2:5">
-      <c r="B45" s="39" t="s">
+      <c r="B45" s="37" t="s">
         <v>178</v>
       </c>
-      <c r="C45" s="39"/>
-      <c r="D45" s="41">
+      <c r="C45" s="37"/>
+      <c r="D45" s="39">
         <v>0.8</v>
       </c>
       <c r="E45" s="25"/>
@@ -6224,42 +6226,42 @@
       <c r="D46" s="25"/>
       <c r="E46" s="25"/>
     </row>
-    <row r="47" spans="2:5">
-      <c r="B47" s="38" t="s">
+    <row r="47" ht="16" spans="2:5">
+      <c r="B47" s="36" t="s">
         <v>141</v>
       </c>
-      <c r="C47" s="38"/>
-      <c r="D47" s="38" t="s">
+      <c r="C47" s="36"/>
+      <c r="D47" s="36" t="s">
         <v>144</v>
       </c>
       <c r="E47" s="25"/>
     </row>
     <row r="48" spans="2:5">
-      <c r="B48" s="39" t="s">
+      <c r="B48" s="37" t="s">
         <v>142</v>
       </c>
-      <c r="C48" s="39"/>
-      <c r="D48" s="41">
+      <c r="C48" s="37"/>
+      <c r="D48" s="39">
         <v>0.8</v>
       </c>
       <c r="E48" s="25"/>
     </row>
     <row r="49" spans="2:5">
-      <c r="B49" s="39" t="s">
+      <c r="B49" s="37" t="s">
         <v>179</v>
       </c>
-      <c r="C49" s="39"/>
-      <c r="D49" s="41">
+      <c r="C49" s="37"/>
+      <c r="D49" s="39">
         <v>1</v>
       </c>
       <c r="E49" s="25"/>
     </row>
     <row r="50" spans="2:5">
-      <c r="B50" s="39" t="s">
+      <c r="B50" s="37" t="s">
         <v>180</v>
       </c>
-      <c r="C50" s="39"/>
-      <c r="D50" s="41">
+      <c r="C50" s="37"/>
+      <c r="D50" s="39">
         <v>1.2</v>
       </c>
       <c r="E50" s="25"/>
@@ -6267,50 +6269,50 @@
     <row r="51" spans="5:5">
       <c r="E51" s="25"/>
     </row>
-    <row r="52" spans="2:5">
-      <c r="B52" s="48" t="s">
+    <row r="52" ht="16" spans="2:5">
+      <c r="B52" s="46" t="s">
         <v>181</v>
       </c>
-      <c r="C52" s="48"/>
-      <c r="D52" s="48" t="s">
+      <c r="C52" s="46"/>
+      <c r="D52" s="46" t="s">
         <v>182</v>
       </c>
       <c r="E52" s="25"/>
     </row>
     <row r="53" spans="2:5">
-      <c r="B53" s="43" t="s">
-        <v>43</v>
-      </c>
-      <c r="C53" s="43" t="s">
+      <c r="B53" s="41" t="s">
+        <v>43</v>
+      </c>
+      <c r="C53" s="41" t="s">
         <v>183</v>
       </c>
-      <c r="D53" s="45">
+      <c r="D53" s="43">
         <f>1/3</f>
         <v>0.333333333333333</v>
       </c>
       <c r="E53" s="25"/>
     </row>
     <row r="54" spans="2:5">
-      <c r="B54" s="43" t="s">
+      <c r="B54" s="41" t="s">
         <v>49</v>
       </c>
-      <c r="C54" s="43" t="s">
+      <c r="C54" s="41" t="s">
         <v>184</v>
       </c>
-      <c r="D54" s="45">
+      <c r="D54" s="43">
         <f>2/3</f>
         <v>0.666666666666667</v>
       </c>
       <c r="E54" s="25"/>
     </row>
     <row r="55" spans="2:5">
-      <c r="B55" s="43" t="s">
+      <c r="B55" s="41" t="s">
         <v>185</v>
       </c>
-      <c r="C55" s="43" t="s">
+      <c r="C55" s="41" t="s">
         <v>186</v>
       </c>
-      <c r="D55" s="45">
+      <c r="D55" s="43">
         <f>1/1</f>
         <v>1</v>
       </c>
@@ -6320,56 +6322,56 @@
       <c r="D56" s="25"/>
       <c r="E56" s="25"/>
     </row>
-    <row r="57" spans="2:5">
-      <c r="B57" s="48" t="s">
+    <row r="57" ht="16" spans="2:5">
+      <c r="B57" s="46" t="s">
         <v>187</v>
       </c>
-      <c r="C57" s="48"/>
-      <c r="D57" s="48" t="s">
+      <c r="C57" s="46"/>
+      <c r="D57" s="46" t="s">
         <v>182</v>
       </c>
       <c r="E57" s="25"/>
     </row>
     <row r="58" spans="2:5">
-      <c r="B58" s="43" t="s">
-        <v>44</v>
-      </c>
-      <c r="C58" s="43" t="s">
+      <c r="B58" s="41" t="s">
+        <v>44</v>
+      </c>
+      <c r="C58" s="41" t="s">
         <v>188</v>
       </c>
-      <c r="D58" s="45">
+      <c r="D58" s="43">
         <f>1/1</f>
         <v>1</v>
       </c>
-      <c r="E58" s="49" t="s">
+      <c r="E58" s="51" t="s">
         <v>189</v>
       </c>
     </row>
     <row r="59" spans="2:5">
-      <c r="B59" s="43" t="s">
+      <c r="B59" s="41" t="s">
         <v>69</v>
       </c>
-      <c r="C59" s="43" t="s">
+      <c r="C59" s="41" t="s">
         <v>190</v>
       </c>
-      <c r="D59" s="45">
+      <c r="D59" s="43">
         <v>0.8</v>
       </c>
-      <c r="E59" s="49" t="s">
+      <c r="E59" s="51" t="s">
         <v>189</v>
       </c>
     </row>
     <row r="60" spans="2:5">
-      <c r="B60" s="43" t="s">
+      <c r="B60" s="41" t="s">
         <v>191</v>
       </c>
-      <c r="C60" s="43" t="s">
+      <c r="C60" s="41" t="s">
         <v>192</v>
       </c>
-      <c r="D60" s="45">
+      <c r="D60" s="43">
         <v>0.2</v>
       </c>
-      <c r="E60" s="49" t="s">
+      <c r="E60" s="51" t="s">
         <v>189</v>
       </c>
     </row>
@@ -6377,88 +6379,88 @@
       <c r="D61" s="25"/>
       <c r="E61" s="25"/>
     </row>
-    <row r="62" spans="2:5">
-      <c r="B62" s="48" t="s">
+    <row r="62" ht="16" spans="2:5">
+      <c r="B62" s="46" t="s">
         <v>11</v>
       </c>
-      <c r="C62" s="48"/>
-      <c r="D62" s="48" t="s">
+      <c r="C62" s="46"/>
+      <c r="D62" s="46" t="s">
         <v>182</v>
       </c>
       <c r="E62" s="25"/>
     </row>
     <row r="63" s="23" customFormat="1" spans="1:5">
-      <c r="A63" s="50"/>
-      <c r="B63" s="43" t="s">
+      <c r="A63" s="47"/>
+      <c r="B63" s="41" t="s">
         <v>51</v>
       </c>
-      <c r="C63" s="43" t="s">
+      <c r="C63" s="41" t="s">
         <v>193</v>
       </c>
-      <c r="D63" s="51">
+      <c r="D63" s="48">
         <v>7</v>
       </c>
-      <c r="E63" s="49" t="s">
+      <c r="E63" s="51" t="s">
         <v>194</v>
       </c>
     </row>
     <row r="64" s="23" customFormat="1" spans="1:5">
-      <c r="A64" s="50"/>
-      <c r="B64" s="43" t="s">
+      <c r="A64" s="47"/>
+      <c r="B64" s="41" t="s">
         <v>195</v>
       </c>
-      <c r="C64" s="43" t="s">
+      <c r="C64" s="41" t="s">
         <v>196</v>
       </c>
-      <c r="D64" s="51">
+      <c r="D64" s="48">
         <v>5</v>
       </c>
-      <c r="E64" s="49" t="s">
+      <c r="E64" s="51" t="s">
         <v>194</v>
       </c>
     </row>
     <row r="65" s="23" customFormat="1" spans="1:5">
-      <c r="A65" s="50"/>
-      <c r="B65" s="43" t="s">
+      <c r="A65" s="47"/>
+      <c r="B65" s="41" t="s">
         <v>54</v>
       </c>
-      <c r="C65" s="43" t="s">
+      <c r="C65" s="41" t="s">
         <v>197</v>
       </c>
-      <c r="D65" s="51">
+      <c r="D65" s="48">
         <v>4</v>
       </c>
-      <c r="E65" s="49" t="s">
+      <c r="E65" s="51" t="s">
         <v>194</v>
       </c>
     </row>
     <row r="66" s="23" customFormat="1" spans="1:5">
-      <c r="A66" s="50"/>
-      <c r="B66" s="43" t="s">
+      <c r="A66" s="47"/>
+      <c r="B66" s="41" t="s">
         <v>47</v>
       </c>
-      <c r="C66" s="43" t="s">
+      <c r="C66" s="41" t="s">
         <v>198</v>
       </c>
-      <c r="D66" s="51">
+      <c r="D66" s="48">
         <v>5</v>
       </c>
-      <c r="E66" s="49" t="s">
+      <c r="E66" s="51" t="s">
         <v>194</v>
       </c>
     </row>
     <row r="67" s="23" customFormat="1" spans="1:5">
-      <c r="A67" s="50"/>
-      <c r="B67" s="43" t="s">
+      <c r="A67" s="47"/>
+      <c r="B67" s="41" t="s">
         <v>42</v>
       </c>
-      <c r="C67" s="43" t="s">
+      <c r="C67" s="41" t="s">
         <v>199</v>
       </c>
-      <c r="D67" s="51">
+      <c r="D67" s="48">
         <v>4</v>
       </c>
-      <c r="E67" s="49" t="s">
+      <c r="E67" s="51" t="s">
         <v>194</v>
       </c>
     </row>
@@ -6568,13 +6570,13 @@
     <tabColor rgb="FFFF0000"/>
   </sheetPr>
   <dimension ref="A1:J13"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8"/>
   <cols>
-    <col min="1" max="1" customWidth="true" width="8.6283185840708" collapsed="false"/>
-    <col min="2" max="2" customWidth="true" width="22.3716814159292" collapsed="false"/>
-    <col min="3" max="3" customWidth="true" width="12.0" collapsed="false"/>
-    <col min="4" max="4" customWidth="true" width="37.4513274336283" collapsed="false"/>
-    <col min="5" max="5" customWidth="true" width="12.0" collapsed="false"/>
+    <col min="1" max="1" width="8.625" customWidth="1"/>
+    <col min="2" max="2" width="22.375" customWidth="1"/>
+    <col min="3" max="3" width="12" customWidth="1"/>
+    <col min="4" max="4" width="37.4519230769231" customWidth="1"/>
+    <col min="5" max="5" width="12" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="40" customHeight="1" spans="1:10">
@@ -6584,159 +6586,159 @@
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
       <c r="D1" s="1"/>
-      <c r="E1" s="2"/>
-      <c r="F1" s="2"/>
-      <c r="G1" s="2"/>
-      <c r="H1" s="2"/>
-      <c r="I1" s="2"/>
-      <c r="J1" s="2"/>
+      <c r="E1" s="19"/>
+      <c r="F1" s="19"/>
+      <c r="G1" s="19"/>
+      <c r="H1" s="19"/>
+      <c r="I1" s="19"/>
+      <c r="J1" s="19"/>
     </row>
     <row r="2" spans="7:8">
-      <c r="G2" s="3"/>
-      <c r="H2" s="3"/>
+      <c r="G2" s="20"/>
+      <c r="H2" s="20"/>
     </row>
     <row r="3" ht="16" customHeight="1" spans="1:4">
-      <c r="A3" s="4"/>
-      <c r="B3" s="4"/>
-      <c r="C3" s="4" t="s">
+      <c r="A3" s="2"/>
+      <c r="B3" s="2"/>
+      <c r="C3" s="2" t="s">
         <v>201</v>
       </c>
-      <c r="D3" s="4" t="s">
+      <c r="D3" s="2" t="s">
         <v>202</v>
       </c>
     </row>
     <row r="4" ht="15" customHeight="1" spans="1:4">
-      <c r="A4" s="5" t="s">
+      <c r="A4" s="3" t="s">
         <v>203</v>
       </c>
-      <c r="B4" s="5"/>
-      <c r="C4" s="6">
+      <c r="B4" s="3"/>
+      <c r="C4" s="4">
         <f>'2. 规模估算'!C5</f>
-        <v>122.6</v>
-      </c>
-      <c r="D4" s="7" t="s">
+        <v>125.266666666666</v>
+      </c>
+      <c r="D4" s="5" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="5" ht="15" customHeight="1" spans="1:4">
-      <c r="A5" s="5" t="s">
+      <c r="A5" s="3" t="s">
         <v>204</v>
       </c>
-      <c r="B5" s="5"/>
-      <c r="C5" s="8">
+      <c r="B5" s="3"/>
+      <c r="C5" s="6">
         <f>'3. 调整因子'!D2</f>
         <v>1.21</v>
       </c>
-      <c r="D5" s="7" t="s">
+      <c r="D5" s="5" t="s">
         <v>205</v>
       </c>
     </row>
     <row r="6" ht="15" customHeight="1" spans="1:7">
-      <c r="A6" s="9" t="s">
+      <c r="A6" s="7" t="s">
         <v>206</v>
       </c>
-      <c r="B6" s="9"/>
-      <c r="C6" s="10">
+      <c r="B6" s="7"/>
+      <c r="C6" s="8">
         <f>C4*C5</f>
-        <v>148.346</v>
-      </c>
-      <c r="D6" s="7" t="s">
+        <v>151.572666666666</v>
+      </c>
+      <c r="D6" s="5" t="s">
         <v>207</v>
       </c>
-      <c r="G6" s="11"/>
+      <c r="G6" s="21"/>
     </row>
     <row r="7" ht="15" customHeight="1" spans="1:7">
-      <c r="A7" s="12" t="s">
+      <c r="A7" s="9" t="s">
         <v>208</v>
       </c>
-      <c r="B7" s="13"/>
-      <c r="C7" s="14">
+      <c r="B7" s="10"/>
+      <c r="C7" s="11">
         <v>10.12</v>
       </c>
-      <c r="D7" s="15" t="s">
+      <c r="D7" s="12" t="s">
         <v>209</v>
       </c>
-      <c r="E7" s="16"/>
-      <c r="F7" s="16"/>
-      <c r="G7" s="11"/>
+      <c r="E7" s="22"/>
+      <c r="F7" s="22"/>
+      <c r="G7" s="21"/>
     </row>
     <row r="8" ht="15" customHeight="1" spans="1:4">
-      <c r="A8" s="17" t="s">
+      <c r="A8" s="13" t="s">
         <v>210</v>
       </c>
-      <c r="B8" s="18"/>
-      <c r="C8" s="8">
+      <c r="B8" s="14"/>
+      <c r="C8" s="6">
         <f>C6*C7/8</f>
-        <v>187.657689999999</v>
-      </c>
-      <c r="D8" s="7" t="s">
+        <v>191.739423333333</v>
+      </c>
+      <c r="D8" s="5" t="s">
         <v>211</v>
       </c>
     </row>
     <row r="9" ht="15" customHeight="1" spans="1:4">
-      <c r="A9" s="19" t="s">
+      <c r="A9" s="15" t="s">
         <v>144</v>
       </c>
-      <c r="B9" s="5" t="s">
+      <c r="B9" s="3" t="s">
         <v>128</v>
       </c>
-      <c r="C9" s="20">
+      <c r="C9" s="16">
         <f>'3. 调整因子'!D3</f>
         <v>1</v>
       </c>
-      <c r="D9" s="21" t="s">
+      <c r="D9" s="17" t="s">
         <v>212</v>
       </c>
     </row>
     <row r="10" ht="15" customHeight="1" spans="1:4">
-      <c r="A10" s="19"/>
-      <c r="B10" s="5" t="s">
+      <c r="A10" s="15"/>
+      <c r="B10" s="3" t="s">
         <v>130</v>
       </c>
-      <c r="C10" s="20">
+      <c r="C10" s="16">
         <f>1+0.025*SUM('3. 调整因子'!D4:D7)</f>
         <v>0.9</v>
       </c>
-      <c r="D10" s="21" t="s">
+      <c r="D10" s="17" t="s">
         <v>213</v>
       </c>
     </row>
     <row r="11" ht="15" customHeight="1" spans="1:4">
-      <c r="A11" s="19"/>
-      <c r="B11" s="5" t="s">
+      <c r="A11" s="15"/>
+      <c r="B11" s="3" t="s">
         <v>139</v>
       </c>
-      <c r="C11" s="20">
+      <c r="C11" s="16">
         <f>'3. 调整因子'!D8</f>
         <v>1</v>
       </c>
-      <c r="D11" s="21" t="s">
+      <c r="D11" s="17" t="s">
         <v>214</v>
       </c>
     </row>
     <row r="12" ht="15" customHeight="1" spans="1:4">
-      <c r="A12" s="19"/>
-      <c r="B12" s="5" t="s">
+      <c r="A12" s="15"/>
+      <c r="B12" s="3" t="s">
         <v>141</v>
       </c>
-      <c r="C12" s="20">
+      <c r="C12" s="16">
         <f>'3. 调整因子'!D9</f>
         <v>0.8</v>
       </c>
-      <c r="D12" s="21" t="s">
+      <c r="D12" s="17" t="s">
         <v>215</v>
       </c>
     </row>
     <row r="13" ht="15" customHeight="1" spans="1:4">
-      <c r="A13" s="17" t="s">
+      <c r="A13" s="13" t="s">
         <v>216</v>
       </c>
-      <c r="B13" s="18"/>
-      <c r="C13" s="22">
+      <c r="B13" s="14"/>
+      <c r="C13" s="18">
         <f>C8*C9*C10*C11*C12</f>
-        <v>135.1135368</v>
-      </c>
-      <c r="D13" s="7" t="s">
+        <v>138.0523848</v>
+      </c>
+      <c r="D13" s="5" t="s">
         <v>217</v>
       </c>
     </row>
